--- a/Anexo 3. Categorización de citas textuales.xlsx
+++ b/Anexo 3. Categorización de citas textuales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carim\Documents\backup ED\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCTAVO SEMESTRE\PROYECTO GUIADO\RSL\PROCESO DE SÍNTESIS\FASE II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73D43B5-606C-47A3-AA05-D0C532081D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEA7715-4653-4C02-BB18-E310E26CFF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="913" activeTab="1" xr2:uid="{C47E371F-1965-4751-ACCB-1213937D35BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="913" activeTab="2" xr2:uid="{C47E371F-1965-4751-ACCB-1213937D35BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos generales" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="834">
   <si>
     <t>ID</t>
   </si>
@@ -338,9 +338,6 @@
   </si>
   <si>
     <t>Etiqueta</t>
-  </si>
-  <si>
-    <t>Síntesis</t>
   </si>
   <si>
     <t>Data Flow Diagram</t>
@@ -770,12 +767,1833 @@
   <si>
     <t>v</t>
   </si>
+  <si>
+    <t>EP-13</t>
+  </si>
+  <si>
+    <t>10.1109/AERO58975.2024.10521100</t>
+  </si>
+  <si>
+    <t>A Demonstration of MBSEsec Applied to Securing Cyber-Physical System Communications</t>
+  </si>
+  <si>
+    <t>Salinger, Gabe and Span, Trae and Chatterjee, Rik and Jepson, Jake and Daily, Jeremy</t>
+  </si>
+  <si>
+    <t>IEEE Xplore</t>
+  </si>
+  <si>
+    <t>2024 IEEE Aerospace Conference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conference </t>
+  </si>
+  <si>
+    <t>Transport protocols;Surveys;Systems architecture;Cyber-physical systems;Systems modeling;Security;Stakeholders</t>
+  </si>
+  <si>
+    <t>The Engineering community is adopting a Digital Engineering approach enabled by Model-Based Systems Engineering (MBSE) as an effective tool for designing complex systems. As technology continues to rapidly advance, security risk mitigation and requirements engineering is becoming a prominent and important factor in the cybersecurity domain. MBSEsec is a security-focused MBSE method using SysML to develop a system architecture that highlights security design considerations. The modeling process used in the MBSEsec method facilitates security requirements and controls elicitation through a structured workflow of specific systems modeling activities. This work illustrates the application of MBSEsec to securing vehicle network transport protocols. The discovery and validation of new exploits that take advantage of vulnerabilities in the data-link layer of the protocol highlights the need to elicit better security requirements for cyber physical systems (CPS). This paper addresses the three pillars of MBSE to secure network architecture, and models five transport protocol vulnerabilities that have been validated and exploited. Using MBSEsec we create security requirements, identify system assets, model threats and risks, and generate security controls for network transport protocols. This work uses heavy vehicle network transport protocol, J1939, as the System of Interest. Using the J1939 network as the SOI for this work allows the models to be supported by and validated with on-vehicle testing. This work contributes a survey of modeling approaches for secure system design, a detailed application of MBSEsec to a CPS network, and illustrates a recommended addition of a new element ‘attacker’ to the MBSEsec profile. This addition, as well as a detailed threat analysis through attack modeling, enables the generation of more accurate, complete, and effective security requirements for preexisting systems.</t>
+  </si>
+  <si>
+    <t>EP-14</t>
+  </si>
+  <si>
+    <t>10.1109/CBD58033.2022.00053</t>
+  </si>
+  <si>
+    <t>A Hybrid Attack Graph Analysis Method based on Model Checking</t>
+  </si>
+  <si>
+    <t>Ge, Yaogang and Shen, Xiaomeng and Xu, Bingfeng and He, Gaofeng</t>
+  </si>
+  <si>
+    <t>2022 Tenth International Conference on Advanced Cloud and Big Data (CBD)</t>
+  </si>
+  <si>
+    <t>Measurement;Analytical models;Cloud computing;Automata;Smart homes;Humidity;Model checking;cyber security;model checking;hybrid attack graph;timed automata;model transformation</t>
+  </si>
+  <si>
+    <t>Attack graph is an essential tool for the security assessment of industrial Internet systems. Unfortunately, the traditional attack graph mainly focuses on discrete information and cannot handle continuous information such as temperature and humidity. These continuous data represent the states of the industrial Internet and are also indicators of attacks, which should be included in the attack graph. To this end, this paper presents a hybrid attack graph model, which can simultaneously describe the discrete and continuous information of the system. Based on the hybrid attack graph model, a security analysis method is presented. Firstly, the transformation rule from hybrid attack graph to timed automata is established. Secondly, the security attribute of the system is described by sequential logic of continuous interval, and then the model checker TACK is used to complete the analysis of the system. Finally, an example is analyzed and verified by a smart home system to illustrate the method’s effectiveness. The method in this paper provides a new idea for attack graph construction and analysis for industrial Internet systems.</t>
+  </si>
+  <si>
+    <t>EP-15</t>
+  </si>
+  <si>
+    <t>10.1109/COMITCon.2019.8862443</t>
+  </si>
+  <si>
+    <t>A Study of Security Modeling Techniques for Smart Systems</t>
+  </si>
+  <si>
+    <t>Tripathi, Dipty and Maurya, Ashish Kumar and Chaturvedi, Amrita and Tripathi, Anil Kumar</t>
+  </si>
+  <si>
+    <t>2019 International Conference on Machine Learning, Big Data, Cloud and Parallel Computing (COMITCon)</t>
+  </si>
+  <si>
+    <t>Security;Unified modeling language;Analytical models;Fault trees;Risk management;Software;Stochastic processes;Smart Systems;Smartness;Security Modeling;Threat Modeling</t>
+  </si>
+  <si>
+    <t>The term “smart” has been used in many ways for describing systems and infrastructure such as smart city, smart home, smart grid, smart meter, etc. These systems may lie in the domain of critical security systems where security can be estimated in terms of confidentiality, integrity and some cases may involve availability for protection against the theft or damage of system resources as well as disruption of the system services. Although, in spite of, being a hot topic to enhance the quality of life, there is no concrete definition of what smart system is and what should be the characteristics of it. Thus, there is a need to identify what these systems actually are and how they can be designed securely. This work firstly attempts to describe attributes related to the smartness to define smart systems. Furthermore, we propose a secure smart system development life cycle, where the security is weaved at all the development phase of smart systems according to principles, guidelines, attack patterns, risk, vulnerability, exploits, and defined rules. Finally, the comparative study is performed for evaluation of traditional security modeling techniques for early assessment of threats and risks in smart systems.</t>
+  </si>
+  <si>
+    <t>EP-16</t>
+  </si>
+  <si>
+    <t>10.1109/ICCCE.2018.8539339</t>
+  </si>
+  <si>
+    <t>A Methodology for Modeling and Analysis of Secure Systems Using Security Patterns and Mitigation Use Cases</t>
+  </si>
+  <si>
+    <t>Maher, Zulfikar Ahmed and Shah, Asadullah and Shaikh, Humaiz and Rahu, Ghulam Ali and Butt, Pinial Khan and Chandio, Shahmurad and Shaikh, Saima</t>
+  </si>
+  <si>
+    <t>2018 7th International Conference on Computer and Communication Engineering (ICCCE)</t>
+  </si>
+  <si>
+    <t>Security;Unified modeling language;Software;Context modeling;Task analysis;Analytical models;Information technology;Security patterns;security pattern modeling;mitigation use cases;secure architecture;secure software design</t>
+  </si>
+  <si>
+    <t>Many approaches for modeling security requirements have been proposed, but software industry did not reach on an agreement on how to express security requirements in a system model or software architecture. The main objective of this perspective paper is to summarize the problem space of representation of security patterns when designing security requirements. Many security patterns are proposed in the literature to help the developers who lack expertise in security to implement it. Application of security patterns has been hindered by the fact that they lack directions for their implementation in a specific scenario. This paper presents a technique for using mitigation use cases for representing solution provided by security patterns. Different challenges and issues were identified related to the application of security patterns in industry.</t>
+  </si>
+  <si>
+    <t>EP-17</t>
+  </si>
+  <si>
+    <t>10.1109/ICACCI.2016.7732430</t>
+  </si>
+  <si>
+    <t>A secure software design methodology</t>
+  </si>
+  <si>
+    <t>Goel, Rajat and Govil, Mahesh Chandra and Singh, Girdhari</t>
+  </si>
+  <si>
+    <t>2016 International Conference on Advances in Computing, Communications and Informatics (ICACCI)</t>
+  </si>
+  <si>
+    <t>Stakeholders;Authorization;Unified modeling language;Permission;Software;Informatics;security requirements;modeling;asset</t>
+  </si>
+  <si>
+    <t>Present times demand security to be an inevitable part of almost any software. To achieve this, the security requirements of the software ought to be efficiently elicited and modeled. The modeling languages available today like Unified Modeling Language (UML) are not efficient enough to model such requirements. Within this research work, a new modeling scheme is presented that first, effectively gathers and analyzes the security concerns of all stakeholders and then represents them through novel diagrams.</t>
+  </si>
+  <si>
+    <t>EP-18</t>
+  </si>
+  <si>
+    <t>10.1109/DASC62030.2024.10749693</t>
+  </si>
+  <si>
+    <t>Airworthiness Security Methods: Modeling and Highlighting Attack Paths in System and Software Architectures for Threat Scenario-Driven Security Analysis</t>
+  </si>
+  <si>
+    <t>Blecken, Marvin and Hintze, Hartmut and Giertzsch, Fabian and God, Ralf</t>
+  </si>
+  <si>
+    <t>2024 AIAA DATC/IEEE 43rd Digital Avionics Systems Conference (DASC)</t>
+  </si>
+  <si>
+    <t>Couplings;Analytical models;Software architecture;Atmospheric modeling;Entertainment industry;Computer architecture;Systems Modeling Language;Software;Security;Risk analysis</t>
+  </si>
+  <si>
+    <t>The digitalization and increased connectivity of aircraft systems not only offer opportunities, such as optimizing business and operational processes as well as the introduction of novel services for passengers, but also pose new security-related risks to the system. As part of the security risks analysis which became mandatory for airworthiness security since the publication of the new certification specification CS-25.1319, threat scenarios and attack paths are defined to enable a more structured identification and assessment of security risks. In order to identify potential attack paths, it is necessary to examine the architectures that were created during the development of the system or the software. These architectures establish the prescribed pathways that an attacker is able to take due to the connection of the architectural elements. However, none of the available approaches for modeling attack paths link the attack paths to the architecture model. In this paper a novel approach for modeling attack paths and linking attack paths to the architecture model is presented. The Systems Modeling Language (SysML)-based approach extends the Risk Analysis and Assessment Modeling Language (RAAML) and introduces elements for modeling attack paths made of various attack actions and vulnerabilities as well as the asset under consideration. Furthermore, relationships are defined to link these attack path elements to the architecture and path segments encompassing the architectural elements. Moreover, the linkage between attack paths and the architectural elements is used to highlight the attack paths in the architectures by using tool-specific capabilities of Cameo Systems Modeler. The approach is exemplarily illustrated taking the example of a seat controller that is connected to the In-Flight Entertainment (IFE) system enabling the adjustment of the seat.</t>
+  </si>
+  <si>
+    <t>EP-19</t>
+  </si>
+  <si>
+    <t>10.1109/DASC43569.2019.9081652</t>
+  </si>
+  <si>
+    <t>Architectural and Behavioral Analysis for Cyber Security</t>
+  </si>
+  <si>
+    <t>Siu, Kit and Moitra, Abha and Li, Meng and Durling, Michael and Herencia-Zapana, Heber and Interrante, John and Meng, Baoluo and Tinelli, Cesare and Chowdhury, Omar and Larraz, Daniel and Yahyazadeh, Moosa and Arif, M. Fareed and Prince, Daniel</t>
+  </si>
+  <si>
+    <t>2019 IEEE/AIAA 38th Digital Avionics Systems Conference (DASC)</t>
+  </si>
+  <si>
+    <t>Threat modeling;Analytical models;Runtime;Instruments;Discharges (electric);Safety;Security;Computer crime;Monitoring;Resilience;cyber security;attack-defense trees;behavioral properties;test cases</t>
+  </si>
+  <si>
+    <t>The asymmetric nature and ever-increasing degree of sophistication of cyber threats drive the need for assurance of critical infrastructure and systems. Current approaches that can help counter these cyber threats include the application of tools with the ability to analyze system behavior in its most general form and in the presence of wide classes of threats-at design time. In this paper we describe our tool for incorporating cyber security resiliency analysis and recommendations in the system design process that are automated, scalable, provide rich feedback, specify trade-offs and are easy to use by system architects. The architecture models and design knowledge are captured in formalisms that are expressive and amenable to automated reasoning, analysis, and analysis for cyber security. The two main components developed are Model-Based Architectural Analysis and Cyber-resiliency Verifier. The Model-Based Architectural Analysis identifies threats against the architecture and the potential tradeoffs of their mitigations. Threats are identified from attack patterns from Mitre's Common Attack Pattern Enumeration and Classification (CAPEC) and defenses are suggested based on controls from NIST's Security and Privacy Controls list. After the threats and defenses are identified, an attack-defense tree is generated along with cutsets that describe attack scenarios and associated defenses. The identified threats as well as the attack-defense trees are visualized to provide a concise and informative view of the analysis. There may be multiple ways of addressing a threat and the system architect can decide which defense to implement. After the architecture has been revised to be secure, we then consider cyber-resiliency behavioral properties of the system. For this we abstract threat models in terms of an instrumentor that incorporates the effects of the threats. This allows us to aggregate classes of threats with the same effect so that they can be addressed at the effect...</t>
+  </si>
+  <si>
+    <t>EP-20</t>
+  </si>
+  <si>
+    <t>10.1109/SoSE50414.2020.9130491</t>
+  </si>
+  <si>
+    <t>Identifying Security Issues with MBSE while Rebuilding Legacy Software Systems</t>
+  </si>
+  <si>
+    <t>Mazeika, Donatas and Butleris, Rimantas</t>
+  </si>
+  <si>
+    <t>2020 IEEE 15th International Conference of System of Systems Engineering (SoSE)</t>
+  </si>
+  <si>
+    <t>Analytical models;Adaptation models;Conferences;Software systems;Security;Complex systems;Guidelines;MBSE;Security Engineering;Legacy system modernization;SysML</t>
+  </si>
+  <si>
+    <t>in this paper, we introduce how Model-based System Engineering (MBSE) could be leveraged in order to tackle security issues while recreating legacy software systems. Originally, MBSE was dedicated to managing the complex system creation in terms of system requirements, design, analysis, verification and validation activities leaving security aspects aside. However, previous research shows that security analysis activity could be integrated into MBSE activity and powerful MBSE tools such as change impact analysis, simulation, validation, and verification could be successfully applied in cross-cutting disciplines. The paper presents guidelines on how and when to apply various security techniques (e.g. security requirements, misuse cases, attack scenarios) in the MBSE environment. The case study demonstrates and proves the adaptability of the security guidelines on the realworld software system modernization project.</t>
+  </si>
+  <si>
+    <t>EP-21</t>
+  </si>
+  <si>
+    <t>10.1109/ISSE51541.2021.9582462</t>
+  </si>
+  <si>
+    <t>Model-based Attack Tree Generation for Cybersecurity Risk-Assessments in Automotive</t>
+  </si>
+  <si>
+    <t>Kern, Matthias and Liu, Bo and Betancourt, Victor Pazmino and Becker, Jürgen</t>
+  </si>
+  <si>
+    <t>2021 IEEE International Symposium on Systems Engineering (ISSE)</t>
+  </si>
+  <si>
+    <t>Systems architecture;Regulation;Risk management;Automobiles;Computer security;Modeling;Standards;Cyber-Security-Risk-Analysis;Attack Tree;Electrical/Electronic-Architecture;Cyber-Physical System</t>
+  </si>
+  <si>
+    <t>Networked and highly automated driver assistance systems require interfaces to the outside world and within the vehicle. These can potentially be used for cybersecurity attacks. Therefore, cybersecurity risk analyses are essential to adequately counter cybersecurity threats. Through UNECE Regulations No. 155, cybersecurity risk assessments, are mandatory for all new cars from 2024. The ISO/SAE 21434 standard “Road vehicles Cybersecurity engineering”, defines requirements for cybersecurity risk management with regard to electrical/electronic systems and components. In this context, it is imperative that possible attack paths are investigated. The creation of these attack paths is labor-intensive and should relate to the preliminary system architecture. Automatic attack tree generation could help to reduce the effort to create attack paths manually. This paper presents a new approach to generate relevant attack paths in a semi-automated way, taking the attack motivation and functional dependencies into account. This can shift the effort of creating attack trees in the concept phase to the preliminary system description and allows cybersecurity experts to focus more on aspects that require their creativity and expertise.</t>
+  </si>
+  <si>
+    <t>EP-22</t>
+  </si>
+  <si>
+    <t>Modeling a SQL injection attack</t>
+  </si>
+  <si>
+    <t>Kaur, Navdeep and Kaur, Parminder</t>
+  </si>
+  <si>
+    <t>2016 3rd International Conference on Computing for Sustainable Global Development (INDIACom)</t>
+  </si>
+  <si>
+    <t>Security;Software;Structured Query Language;Databases;Conferences;Testing;Computational modeling;Requirement Phase;Security Modeling;Secure Software Engineering;Security Requirements;SQL injection</t>
+  </si>
+  <si>
+    <t>Day in day out, the online security attacks are consistently increasing. According to OWASP Top Ten Cheat sheet-2013, SQL Injection (SQLI) is at peak among online attacks. This can be attributed primarily to lack of awareness on software security; skill set shortage, non-availability of right tools to evaluate security as a metric across various phases of SDLC. With the looming deadlines and tight budgets implementing security viewed as a handicap. Many organizations direct their application security efforts on automated detective solutions such as application scans, penetration testing, web application firewalls and patch management rather than preventing the defects from occurring in the first place i.e. during development of web application. The dominating idea, `Secure Software Engineering' saves time as well as cost for mitigating vulnerabilities. Keeping in line with the context of security in software development, this paper focused on mitigating SQL Injection vulnerability in SDLC. The process of SQLI attack is discussed with the help of suitable example. The paper primarily focuses on security actions performed in Requirement Phase for extenuating SQLI. A methodical way of modeling SQLI attacks by using attack trees, VCG, Misuse cases is presented for eliciting security requirements.</t>
+  </si>
+  <si>
+    <t>EP-23</t>
+  </si>
+  <si>
+    <t>10.1109/RAMS48030.2020.9153607</t>
+  </si>
+  <si>
+    <t>A Model-Based Framework for Analyzing the Security of System Architectures</t>
+  </si>
+  <si>
+    <t>Siu, Kit and Herencia-Zapana, Heber and Prince, Daniel and Moitra, Abha</t>
+  </si>
+  <si>
+    <t>2020 Annual Reliability and Maintainability Symposium (RAMS)</t>
+  </si>
+  <si>
+    <t>Security;Atomic measurements;Logic gates;Analytical models;Fault trees;Systems architecture;Safety;attack-defense trees;control measures;model-based design;security;threat analysis</t>
+  </si>
+  <si>
+    <t>We introduce a compositional, model-based framework for modeling, visualizing and analyzing the security of system architectures. This work extends the framework we developed previously for analyzing safety [1]. With this extension, our framework can be used to analyze both safety and security, however this paper focuses on security. The major contribution of this paper is setting the terminology and methodology for building a tree for analyzing the security of a system. Defining precisely the qualitative and quantitative aspects of the tree is very important-just as fault trees are rooted in the theory of probability, we want our tree to be built on solid mathematical foundation. Based on [2] and [3], attack-defense tree is a better representation of a system over attack trees because the latter only captures attack scenarios and does not model the interaction between attacks and the defenses that could be put in place to guard against the attacks. More importantly, security of a system is constantly evolving-as better control measures are put in place, more sophisticated attacks are implemented. Therefore, modeling only attacks without considering the defenses in place is very limiting. Guided by some of the formalisms introduced in [2] [3], we extended their concepts to include guidelines and considerations from DO-326A and DO-356A so that the terminology used in the tree is relevant to the aviation industry. We reference measure theory and order theory to define functions for the quantitative aspects of the tree. We also made sure that the measures were consistent with the intuition of a security design engineer. Finally, we give an example of the modeling language and the attack-defense tree that is automatically generated.</t>
+  </si>
+  <si>
+    <t>EP-24</t>
+  </si>
+  <si>
+    <t>10.1109/HASE.2017.12</t>
+  </si>
+  <si>
+    <t>Quantitative Security and Safety Analysis with Attack-Fault Trees</t>
+  </si>
+  <si>
+    <t>Kumar, Rajesh and Stoelinga, Mariëlle</t>
+  </si>
+  <si>
+    <t>2017 IEEE 18th International Symposium on High Assurance Systems Engineering (HASE)</t>
+  </si>
+  <si>
+    <t>Security;Fault trees;Logic gates;Safety;Unified modeling language;Silicon;Standards;safety-security analysis;model-checking;attack trees;fault trees;industrial case studies</t>
+  </si>
+  <si>
+    <t>Cyber physical systems, like power plants, medical devices and data centers have to meet high standards, both in terms of safety (i.e. absence of unintentional failures) and security(i.e. no disruptions due to malicious attacks). This paper presents attack fault trees (AFTs), a formalism thatmarries fault trees (safety) and attack trees (security). We equipAFTs with stochastic model checking techniques, enabling a rich plethora of qualitative and quantitative analyses. Qualitative metrics pinpoint to root causes of the system failure, while quantitative metrics concern the likelihood, cost, and impact of a disruption. Examples are: (1) the most likely attack path, (2) the most costly system failure, (3) the expected impact of an attack. Each of these metrics can be constrained, i.e., we can provide the most likely disruption within time t and/or budget B. Finally, we can use sensitivity analysis to find the attack step that has the most influence on a given metric. We demonstrate our approach through three realistic cases studies.</t>
+  </si>
+  <si>
+    <t>EP-25</t>
+  </si>
+  <si>
+    <t>10.1109/ICCNC.2016.7440631</t>
+  </si>
+  <si>
+    <t>Network security analyzing and modeling based on Petri net and Attack tree for SDN</t>
+  </si>
+  <si>
+    <t>Yao, Linyuan and Dong, Ping and Zheng, Tao and Zhang, Hongke and Du, Xiaojiang and Guizani, Mohsen</t>
+  </si>
+  <si>
+    <t>2016 International Conference on Computing, Networking and Communications (ICNC)</t>
+  </si>
+  <si>
+    <t>Switches;Security;Petri nets;Analytical models;Data communication;Network topology;Control;Forward;Separation;Petri net;Attack tree;OpenFlow;SDN</t>
+  </si>
+  <si>
+    <t>Due to the widespread research on Software Defined Networks (SDNs), its security has received much attention recently. But most of those attempts consider SDN security from the OpenFlow perspective. To the best of our knowledge, none so far has paid attention to the security analysis and modeling of Forwarding and Control planes Separation Network Structure (FCSNS) in SDN. Therefore, this paper provides a different approach to network security based on Petri net and Attack tree models. Our objective is to analyze the FCSNS security via the combination of model and state. This method represents the network structure and state transferring by way of Petri net. In addition, it introduces the security analysis method of STRIDE to build up the Attack tree model. Finally, we analyze FCSNS via the combination of Petri net and Attack tree model and present the results. Our results are very promising in using such models to achieve such security objectives.</t>
+  </si>
+  <si>
+    <t>EP-26</t>
+  </si>
+  <si>
+    <t>10.1109/OJCS.2024.3520315</t>
+  </si>
+  <si>
+    <t>Quantitative Cybersecurity Analysis Framework for Cyber Physical Systems: A Conceptual Approach</t>
+  </si>
+  <si>
+    <t>Abdulhamid, Alhassan and Kabir, Sohag and Ghafir, Ibrahim and Lei, Ci and Hindi, Khalil El and Hammoudeh, Mohammad</t>
+  </si>
+  <si>
+    <t>IEEE Open Journal of the Computer Society</t>
+  </si>
+  <si>
+    <t>Journal</t>
+  </si>
+  <si>
+    <t>Security;Computational modeling;Uncertainty;Fuzzy logic;Analytical models;Data models;Costs;Biological system modeling;Adaptation models;Computer architecture;Attack tree;Bayesian networks;cyber-physical systems (CPS);expert judgement;fuzzy logic system;security analysis</t>
+  </si>
+  <si>
+    <t>Cyber-physical systems (CPS) are indispensable in various sectors, enabling convenient and efficient processes in today's rapidly evolving technological landscape. However, the integration of internet-enabled components with physical processes exposes CPS to numerous security threats, rendering them susceptible to potential cyber-attacks. This paper presents a quantitative analysis framework for evaluating the security attributes of CPS conceptual design. Focusing on CPS design architecture, the framework models and quantifies security attributes by considering various dimensions. The paper demonstrates the integration of qualitative expert inputs into a fuzzy logic system to address the challenges and uncertainties associated with vulnerability data in CPS security quantification. Additionally, it examines the statistical dependence of basic attack steps (BASs) and their impact on the overall system security analysis, taking into account the intricate connectivity of CPS and the vulnerabilities that attackers could exploit. The novelty of the proposed framework lies in its integrated approach to modelling and quantifying cybersecurity attributes in the CPS environment while considering uncertainties in vulnerability data and dependencies between security events. The computation of statistical and stochastic dependencies among BASs is achieved by mapping the attack tree (AT) to a higher statistical model of the Bayesian network (BN) model. The application of this framework was demonstrated using an intelligent glucose monitoring and insulin administration system (IGMIAS). The framework's general nature makes it adaptable for quantifying cybersecurity behaviours in any CPS environment.</t>
+  </si>
+  <si>
+    <t>EP-27</t>
+  </si>
+  <si>
+    <t>10.1109/ICPICS58376.2023.10235341</t>
+  </si>
+  <si>
+    <t>Research on Edge Security Analysis Method Based on Decision Tree</t>
+  </si>
+  <si>
+    <t>Wang, Zhe and Wang, Hui and Li, Dejian and Zhao, Jian and Yan, Tianyu and Wu, Tiantian</t>
+  </si>
+  <si>
+    <t>2023 IEEE 5th International Conference on Power, Intelligent Computing and Systems (ICPICS)</t>
+  </si>
+  <si>
+    <t>Performance evaluation;Machine learning algorithms;Computational modeling;Machine learning;Real-time systems;Classification algorithms;Security;edge security analysis;decision tree;machine learning;algorithm model</t>
+  </si>
+  <si>
+    <t>Based on the classification of ack, udp, and syn type abnormal traffic launched by worm programs, machine learning algorithms are used to achieve real-time classification of traffic generated by terminal devices, without affecting the normal business traffic of the terminal. After project evaluation and comparison of the performance of several classification and clustering models, the current model in the project is an algorithm implementation of decision tree type. Through experiments, it has been proven that the edge security analysis method based on decision trees is effective.</t>
+  </si>
+  <si>
+    <t>EP-28</t>
+  </si>
+  <si>
+    <t>10.1109/SoutheastCon51012.2023.10115120</t>
+  </si>
+  <si>
+    <t>Security Analysis of a Smart City Traffic Control System using a Threat Model-based Approach</t>
+  </si>
+  <si>
+    <t>Alshamrani, Saeed and Hasan, Ragib</t>
+  </si>
+  <si>
+    <t>SoutheastCon 2023</t>
+  </si>
+  <si>
+    <t>Threat modeling;Smart cities;Transportation;Traffic control;Privacy breach;Sensor systems;Robustness;threat model;smart cities;traffic control systems</t>
+  </si>
+  <si>
+    <t>In recent years, smart cities have become more commonplace, with technologies such as smart traffic control systems and outdoor sensors widely used in many places. However, there are numerous security issues that threaten the safety of such systems. It is important to analyze the security of such systems in order to make them robust and ensure the security of smart cities. Threat modeling is a process used to identify potential risks and vulnerabilities in a system. In this paper, we will develop a threat model and security analysis for a smart traffic control system. This analysis and the threat model will allow researchers and developers to identify security issues in smart city traffic control systems and develop effective mitigation strategies.</t>
+  </si>
+  <si>
+    <t>EP-29</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jii.2023.100465</t>
+  </si>
+  <si>
+    <t>A model-based methodology to support systems security design and assessment</t>
+  </si>
+  <si>
+    <t>Avi Shaked</t>
+  </si>
+  <si>
+    <t>ScienceDirect</t>
+  </si>
+  <si>
+    <t>Journal of Industrial Information Integration</t>
+  </si>
+  <si>
+    <t>Model-based design, Systems security engineering, Systems specification methodology, Modeling methodology, Threat and risk assessment</t>
+  </si>
+  <si>
+    <t>Addressing cybersecurity aspects while designing systems is challenging. As our systems increasingly rely on digital technology to perform, security and resilience aspects need to be considered during the system design process. However, the integration of pertinent information into the systems engineering lifecycle is not trivial, as it is characterized by following verbose guidelines and documentation, and has no practical, model-based methodology to support threat-aware design of systems. In this article, we address this gap by presenting an integrative, model-based methodology to support the design and assessment of systems' security aspects. We discuss the methodology's design, specifically with respect to system development scenarios, and detail industrial case studies demonstrating the applicability of the methodology.</t>
+  </si>
+  <si>
+    <t>EP-30</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ress.2019.106773</t>
+  </si>
+  <si>
+    <t>Combined automotive safety and security pattern engineering approach</t>
+  </si>
+  <si>
+    <t>H. Martin and Z. Ma and Ch. Schmittner and B. Winkler and M. Krammer and D. Schneider and T. Amorim and G. Macher and Ch. Kreiner</t>
+  </si>
+  <si>
+    <t>Reliability Engineering &amp; System Safety</t>
+  </si>
+  <si>
+    <t>ISO 26262, SAE J3061, Engineering workflow, Safety pattern, Security pattern, Automotive</t>
+  </si>
+  <si>
+    <t>Automotive systems will exhibit increased levels of automation as well as ever tighter integration with other vehicles, traffic infrastructure, and cloud services. From safety perspective, this can be perceived as boon or bane - it greatly increases complexity and uncertainty, but at the same time opens up new opportunities for realizing innovative safety functions. Moreover, cybersecurity becomes important as additional concern because attacks are now much more likely and severe. However, there is a lack of experience with security concerns in context of safety engineering in general and in automotive safety departments in particular. To address this problem, we propose a systematic pattern-based approach that interlinks safety and security patterns and provides guidance with respect to selection and combination of both types of patterns in context of system engineering. A combined safety and security pattern engineering workflow is proposed to provide systematic guidance to support non-expert engineers based on best practices. The application of the approach is shown and demonstrated by an automotive case study and different use case scenarios.</t>
+  </si>
+  <si>
+    <t>EP-31</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.cose.2018.03.016</t>
+  </si>
+  <si>
+    <t>Engineering secure systems: Models, patterns and empirical validation</t>
+  </si>
+  <si>
+    <t>Brahim Hamid and Donatus Weber</t>
+  </si>
+  <si>
+    <t>Computers &amp; Security</t>
+  </si>
+  <si>
+    <t>Security, System engineering, Pattern, Meta-modeling, Model driven engineering</t>
+  </si>
+  <si>
+    <t>Several development approaches have been proposed to handle the growing complexity of software system design. The most popular methods use models as the main artifacts to construct and maintain. The desired role of such models is to facilitate, systematize and standardize the construction of software-based systems. In our work, we propose a model-driven engineering (MDE) methodological approach associated with a pattern-based approach to support the development of secure software systems. We address the idea of using patterns to describe solutions for security as recurring security problems in specific design contexts and present a well-proven generic scheme for their solutions. The proposed approach is based on metamodeling and model transformation techniques to define patterns at different levels of abstraction and generate different representations according to the target domain concerns, respectively. Moreover, we describe an operational architecture for development tools to support the approach. Finally, an empirical evaluation of the proposed approach is presented through a practical application to a use case in the metrology domain with strong security requirements, which is followed by a description of a survey performed among domain experts to better understand their perceptions regarding our approach.</t>
+  </si>
+  <si>
+    <t>EP-32</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jss.2024.112144</t>
+  </si>
+  <si>
+    <t>GDPR compliance via software evolution: Weaving security controls in software design</t>
+  </si>
+  <si>
+    <t>Vanessa Ayala-Rivera and A. Omar Portillo-Dominguez and Liliana Pasquale</t>
+  </si>
+  <si>
+    <t>Journal of Systems and Software</t>
+  </si>
+  <si>
+    <t>Software evolution, Privacy and security, Software design, Data protection, GDPR, Compliance</t>
+  </si>
+  <si>
+    <t>Software should comply with international privacy laws, like the General Data Protection Regulation (GDPR). However, implementing appropriate technical controls is often an error-prone and time-consuming process. This is partly due to the limited knowledge of software engineers about privacy and security. This paper proposes SoCo, a semi-automated approach to support organizations in achieving software compliance with the GDPR data protection principles. To do so, SoCo supports engineers in identifying and integrating appropriate technical controls in sequence diagrams during the design phase. SoCo includes a technique to assist engineers to identify data processing activities in software applications modeled as sequence diagrams that may need to comply with the GDPR, a catalog of privacy and security controls that engineers can use to fix non-compliant activities, and a technique to implement such controls in the non-compliant sequence diagrams. Our evaluation results show that SoCo can help software engineers identify and design appropriate security controls to address GDPR violations and required moderate manual effort when applied to a substantive open-source application. Editor’s note: Open Science material was validated by the Journal of Systems and Software Open Science Board.</t>
+  </si>
+  <si>
+    <t>EP-33</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.cose.2023.103639</t>
+  </si>
+  <si>
+    <t>Secure software development and testing: A model-based methodology</t>
+  </si>
+  <si>
+    <t>Valentina Casola and Alessandra {De Benedictis} and Carlo Mazzocca and Vittorio Orbinato</t>
+  </si>
+  <si>
+    <t>Secure software development, SecDevOps methodology, DevSecOps methodology, Model-based testing, Automated security testing plan generation, Secure containerized microservice applications</t>
+  </si>
+  <si>
+    <t>Modern industries widely rely upon software and IT services, in a context where cybercrime is rapidly spreading in more and more sectors. Unfortunately, despite greater general awareness of security risks and the availability of security tools that can help to cope with those risks, many organizations (especially medium/small-size ones) still lag when it comes to building security into their services. This is mainly due to the limited security skills of common developers/IT project managers and to the typically high costs of security procedures. In fact, while automated tools exist to perform code analysis, vulnerability scanning, or security testing, the manual intervention of security experts is still required not only for security analysis and design, but also to configure and elaborate the output of the security testing tools. In this paper, we propose a novel secure software development methodology aimed at supporting developers from security design to security testing, suitable for integration within modern DevOps pipelines according to a DevSecOps (or SecDevOps) approach. The proposed methodology leverages a model-based process that enables identifying existing threats, selecting appropriate countermeasures to enforce, and verify their mitigation effectiveness through both static assessment procedures and targeted security tests. To demonstrate our approach's feasibility and concretely illustrate the devised activities, we provide a step-by-step description of the whole process concerning a containerized microservice-based application case study. In addition, we discuss the application of the proposed methodology, in its threat modeling and security testing phases, to a well-known vulnerable web application widely used for security training purposes, to illustrate that we can identify most of the existing vulnerabilities and determine appropriate test plans to assess and mitigate such vulnerabilities.</t>
+  </si>
+  <si>
+    <t>EP-34</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.cose.2016.09.001</t>
+  </si>
+  <si>
+    <t>Security knowledge representation artifacts for creating secure IT systems</t>
+  </si>
+  <si>
+    <t>Jose Fran. Ruiz and Marcos Arjona and Antonio Maña and Carsten Rudolph</t>
+  </si>
+  <si>
+    <t>Security engineering process, Security modeling, Security solutions, Domain specific tools, Security requirements</t>
+  </si>
+  <si>
+    <t>The creation of secure applications is more than ever a complex task because it requires from system engineers increasing levels of knowledge in security requirements, design and implementation. In fact, the fast increasing size and volatility of this knowledge has reached a point in which it is unrealistic to expect that system engineers can keep up to date with it. The most prominent paradigm for addressing this problem is the use of security patterns to communicate security knowledge from experts to system designers. This, and other security artifacts, have proved their utility and benefits in the past years, improving the way security is taken into account by system engineers and developers. On the other hand, these artifacts have some limitations that have prevented them from becoming more widespread. In particular, security patterns are human-oriented and as such heavily based on natural language, which implies intrinsic high degrees of imprecision and ambiguity. In our opinion, we need to make the move from purely human-oriented artifacts to hybrid artifacts that convey information for both humans (engineers and designers) and computer tools (engineering and development environments). Therefore, we have created a new security knowledge representation artifact that aims to cover the needs of system engineers and help them not only in applying a solution, but also in understanding the security aspects of a given domain as a highly-related set of security concepts (e.g. properties, requirements, solutions, etc.). This artifact, called Domain Security Metamodel (DSM), is, as its name suggests, domain-specific and contains information about all security aspects that are relevant in a specific domain (e.g. embedded systems, web services, etc.). The DSM contains security solutions that implement the security properties of the specific domains. That way, when users apply them into their system models the solutions for development time can be integrated directly and naturally. In order to describe our approach in a useful way we use a running example based on the Web Service Security (WS-Security) specification.</t>
+  </si>
+  <si>
+    <t>EP-35</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s43926-022-00027-w</t>
+  </si>
+  <si>
+    <t>A framework for evaluating security risk in system design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul A. Wortman &amp; John A. Chandy </t>
+  </si>
+  <si>
+    <t>SpringerLink</t>
+  </si>
+  <si>
+    <t>Discover Internet of Things</t>
+  </si>
+  <si>
+    <t>System security modeling
+Security risk analysis
+Security metrics
+Security design exploration</t>
+  </si>
+  <si>
+    <t>Design and development of ubiquitous computer network systems has become increasingly difficult as technology continues to grow. From the introduction of new technologies to the discovery of existing threats, weaknesses, and vulnerabilities there is a constantly changing landscape of potential risks and rewards. The cyber security community, and industry at large, is learning to account for these increasing threats by including protections and mitigations from the beginning of the design V process. However, issues still come from limitations in time for thoroughly exploring a potential design space and the knowledge base required to easily account for potential vulnerabilities in each. To address this problem we propose the G-T-S framework, which is an automated tool that allows a user to provide a set of inputs relating to the desired design space and returns a monetary security risk evaluation of each. This methodology first generates a series of potential designs, then dissects their contents to associate possible vulnerabilities to device elements, and finally evaluates the security risk poised to a central asset of importance. We exemplify the tools, provide methodologies for required background research, and discuss the results in evaluating a series of IoT Home models using the GTS framework. Through implementation of our framework we simplify the information an individual will require to begin the design process, lower the bar for entry to perform evaluating security risk, and present the risk as an easily understood monetary metric.</t>
+  </si>
+  <si>
+    <t>EP-36</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s42979-024-02748-x</t>
+  </si>
+  <si>
+    <t>A Model-Based Systems Engineering Plugin for Cloud Security Architecture Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuri Gil Dantas, Vivek Nigam &amp; Ulrich Schöpp </t>
+  </si>
+  <si>
+    <t>SN Computer Science</t>
+  </si>
+  <si>
+    <t>Securing cloud architectures
+Model-based systems engineering
+Security architecture patterns
+Automation</t>
+  </si>
+  <si>
+    <t>Security is one of the biggest concerns for cloud infrastructures. Cloud infrastructures are susceptible to a wide range of threats, including external and internal threats. Without proper security mechanisms, these threats may compromise the security properties of services hosted in the cloud. To secure cloud infrastructures against threats, it is crucial to perform a threat analysis in the early stages of the system development (i.e., during the design of the system architecture). Threat Analysis and Risk Assessment (TARA) is a well-known approach used by researchers and practitioners. TARA consists of several activities, including asset identification, threat scenarios, attack paths, and risk treatment decision. The risk treatment decision activity involves selecting appropriate security measures to mitigate the identified threat scenarios. In the current state of practice, TARA activities are performed manually by engineers, leading to time-consuming processes and potential errors. In our previous article, we proposed a logic programming tool to enable the automation of TARA activities, including the recommendation of cloud-based security measures. This article proposes Security Pattern Synthesis, a Model-Based Systems Engineering (MBSE) plugin for securing cloud architectures. Security Pattern Synthesis is implemented in Java while using the previously proposed logic-programming tool as a backend to reason about the security of the cloud architecture.</t>
+  </si>
+  <si>
+    <t>EP-37</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s42400-022-00109-w</t>
+  </si>
+  <si>
+    <t>Abstract security patterns and the design of secure systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eduardo B. Fernandez, Nobukazu Yoshioka, Hironori Washizaki &amp; Joseph Yoder </t>
+  </si>
+  <si>
+    <t>Cybersecurity</t>
+  </si>
+  <si>
+    <t>Security patterns
+Secure software development
+Security requirements
+Secure software architecture
+IoT systems design</t>
+  </si>
+  <si>
+    <t>During the initial stages of software development, the primary goal is to define precise and detailed requirements without concern for software realizations. Security constraints should be introduced then and must be based on the semantic aspects of applications, not on their software architectures, as it is the case in most secure development methodologies. In these stages, we need to identify threats as attacker goals and indicate what conceptual security defenses are needed to thwart these goals, without consideration of implementation details. We can consider the effects of threats on the application assets and try to find ways to stop them. These threats should be controlled with abstract security mechanisms that can be realized by abstract security patterns (ASPs), that include only the core functions of these mechanisms, which must be present in every implementation of them. An abstract security pattern describes a conceptual security mechanism that includes functions able to stop or mitigate a threat or comply with a regulation or institutional policy. We describe here the properties of ASPs and present a detailed example. We relate ASPs to each other and to Security Solution Frames, which describe families of related patterns. We show how to include ASPs to secure an application, as well as how to derive concrete patterns from them. Finally, we discuss their practical value, including their use in “security by design” and IoT systems design.</t>
+  </si>
+  <si>
+    <t>EP-38</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10270-025-01328-8</t>
+  </si>
+  <si>
+    <t>An approach to generating attack graphs and analyzing threats based on CAPEC and ATT&amp;CK matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changlan Fu, He Zhang &amp; Yaochen Zhou </t>
+  </si>
+  <si>
+    <t>Software and Systems Modeling</t>
+  </si>
+  <si>
+    <t>Threat modeling
+Meta attack language
+Attack graph model
+Attack paths</t>
+  </si>
+  <si>
+    <t>Threat modeling based on attack graphs can be used to understand and evaluate system security, and has become an important means of enterprise system security protection. However, existing approaches suffer from several major drawbacks: (a) insufficient automation and extensibility, (b) insufficient coverage of the generated attack graph for threats, and (c) incomplete threat analysis. Therefore, we are motivated to propose an approach for generating attack graphs and analyzing threats. First, we design an automatic attack graph generation model based on Common Attack Pattern Enumeration and Classification (CAPEC) and MITRE ATT&amp;CK Matrix. The model is implemented using the Meta Attack Language to ensure the extensibility of model rules. Second, we use the attack chain analysis method to construct the automatic generation model, and map the attack patterns, techniques and tactics involved in the attack chain to the corresponding attack patterns in CAPEC and ATT&amp;CK framework, so as to improve the coverage of the generated attack graph to threats. Third, we propose an approach for attack path analysis. The process of this approach includes attack graph structure optimization, node evaluation, attack simulation and mitigation measure generation, which can infer a list of attack paths sorted by risk degree. A tool supporting the approach is also proposed. This paper evaluates the proposed approach and tool through illustrative exemplars and comparative studies. The results show that this approach can effectively support users to threat modeling for large systems, and attack graph analysis results can assist enterprise users to make effective security decisions.</t>
+  </si>
+  <si>
+    <t>EP-39</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10207-025-01082-4</t>
+  </si>
+  <si>
+    <t>xT-STRIDE threat model for unmanned air vehicle security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aytac Ugur Yerden, Sinan Senol, Mehmet Kara &amp; Savas Dilibal </t>
+  </si>
+  <si>
+    <t>International Journal of Information Security</t>
+  </si>
+  <si>
+    <t>UAV
+Internet of Things
+Cybersecurity
+Threat modeling
+STRIDE</t>
+  </si>
+  <si>
+    <t>In recent years, substantial progress has been made in the design and development of unmanned aerial vehicles (UAVs) with diverse functional capabilities for avionic applications. Beyond addressing performance bottlenecks, the growing threat of cybersecurity attacks introduces additional complexity to the UAV design process. Developing a high-performance UAV system involves navigating technical security challenges that must be addressed pragmatically. Implementing excessive security measures can increase costs and degrade system performance, while insufficient protection of vulnerable components may expose the UAV to potential exploitation. This study introduces a multi-layered drone system, thoroughly examines threats to its components, and outlines corresponding safeguards in trusted layers. The security requirements for UAV systems were defined using the Common Criteria framework. To strengthen UAV security under real-world operational conditions, a novel threat modeling approach, xT-STRIDE, has been developed. This method incorporates the UAV’s communication and embedded system architecture, modeled with realistic security elements. The xT-STRIDE framework was evaluated theoretically in conjunction with traditional threat modeling techniques.</t>
+  </si>
+  <si>
+    <t>"Fig. 3 illustrates the security requirements diagram that was generated for the ECUs on the truck network."</t>
+  </si>
+  <si>
+    <t>Diagrama de requisitos de seguridad, Diagrama de definición de bloques, Diagrama de actividades, Diagrama de casos de mal uso</t>
+  </si>
+  <si>
+    <t>"Fig.4 illustrates the complete structure and asset definition for the truck network. After the stereotypes were applied, the security requirements were allocated to the appropriate system assets."</t>
+  </si>
+  <si>
+    <t>"Fig. 5 displays the Threat and Risk Definition diagram that was created for the system. The risk associated with this system can be defined as ”An attacker is able to disrupt normal functions of an ECU by tampering with its operations via various malicious message attacks”, which is applicable to all system assets on the network."</t>
+  </si>
+  <si>
+    <t>"The activity diagrams are comprised of swim lanes that represent the behavior of each actor within the scenario. Fig. 6 illustrates the attack scenario for the connection exhaustion attack."</t>
+  </si>
+  <si>
+    <t>"If an inappropriate number of packets is sent or received, the connection is terminated. We note that this adds additional complexity to the process, but the security benefits outweigh this concern. The Validate and Sanitize incoming messages security control is illustrated in Fig. 7."</t>
+  </si>
+  <si>
+    <t>pág. 10</t>
+  </si>
+  <si>
+    <t>"This phase consists of modeling both behavior a land structural security specifications. For behavioral risk and threat definition, a Misuse Case diagram (Appendix A, Fig. 8) was developed to describe the goals of a system from the perspective of the users of the system, as well as the goals of the misuser to exploit the system."</t>
+  </si>
+  <si>
+    <t>"Attack graph is an essential tool for the security  assessment of industrial Internet systems."</t>
+  </si>
+  <si>
+    <t>Attack Graph</t>
+  </si>
+  <si>
+    <t>"The attack graph used to analyze the security of such systems must be able to describe both discrete and continuous information. Therefore, the hybrid attack graph (HAG) model has been proposed to support the security analysis of such industrial Internet systems."</t>
+  </si>
+  <si>
+    <t>"Misuse case diagram specifies the unwanted behavior to define what systems should not do in the proposed system with the negative use case in comparison of positive use cases [8]. It extends UML use cases for describing functions that a system should not be able to perform with additional stereotyped relationships, e.g., prevents and deducts to represent potential security flaws and its prevention."</t>
+  </si>
+  <si>
+    <t>Misuse Case, Abuse Case, Fault Tree, Attack Tree, Priviledge Graph, Petri Net, Bayesian Networkes</t>
+  </si>
+  <si>
+    <t>"Abuse cases [9], [10] are another variant of UML use cases that are complementary to misuse cases. They facilitate requirement modeling, design and testing of systems for security engineering. It finds a range of security privileges vulnerable to be abused with the specification of attack and its consequences from the attacker point of view and intended reaction of the system for illegitimate use."</t>
+  </si>
+  <si>
+    <t>"FT [15], [16] is a deductive methodology used to analyze the undesired event and its causes with conditions by constructing a tree where an event is mapped on root node (e.g., a system failure) and causes or conditions of the event are mapped at leaf nodes. It may traditionally use for modeling of system reliability. Although, it can be used for security modeling as well."</t>
+  </si>
+  <si>
+    <t>"Attack trees are introduced to overcome the limitations of fault trees. Attack tree [19] describes how an attacker can achieve attack goal against any system. These are the logical graph model, a function of atomic attacks that analyze the security using “what if” game, i.e., observed the effect and its causes. A security breach or attack goal is represented as a root node whereas atomic attacks are represented by leaf nodes."</t>
+  </si>
+  <si>
+    <t>"The graph models the possible vulnerability that can be exploited to defeat the security goals of the system. The nodes represent the set of privileges assigned to users and arc represents the vulnerability. The existence of arc between two nodes A, B shows the user with privilege A obtained the privilege of B using some techniques"</t>
+  </si>
+  <si>
+    <t>"Petri net [22], [23] is a mathematical tool to model concurrent, asynchronous and distributed processes [24], [25], [26]. It is a directed bipartite graph consists of place and transition to represent states (circles) and actions or events (bar) respectively."</t>
+  </si>
+  <si>
+    <t>"The theory supports the identification and classification of threat class with supervised or unsupervised learning and accumulates the threat resisting approach to ensure security"</t>
+  </si>
+  <si>
+    <t>"A mitigation use case is simply an extended use case from the point of view of showing mitigation scenario for protecting the system from malicious attacks from different actors. In [34] authors used use case, misuse case and mitigation use case’s descriptions to generate test cases for the system for integration of security characteristics into throughout the system development life cycle from requirements phase to the testing phase. [35] integrated use case model with use, misuse, and mitigation use case to show what use cases are threatened and how they will be mitigated using mitigation use cases in a single view."</t>
+  </si>
+  <si>
+    <t>Mitigation Use Case, Misuse Case</t>
+  </si>
+  <si>
+    <t>"In this paper, rank-based diagrams are proposed to model the security requirements. Unlike UML, these diagrams follow a formal requirement elicitation and assessment mechanism."</t>
+  </si>
+  <si>
+    <t>Diagramas basados en rangos</t>
+  </si>
+  <si>
+    <t>"As part of the security risks analysis which became mandatory for airworthiness security since the publication of the new certification specification CS-25.1319, threat scenarios and attack paths are defined to enable a more structured identification and assessment of security risks."</t>
+  </si>
+  <si>
+    <t>Attack Paths Diagram</t>
+  </si>
+  <si>
+    <t>"Fig. 6. Attack path modeling library extending RAAML"</t>
+  </si>
+  <si>
+    <t>"Fig. 10. Attack path model and linkage to multi-system model"</t>
+  </si>
+  <si>
+    <t>"Fig. 12. Attack path highlighting in multi-system architecture"</t>
+  </si>
+  <si>
+    <t>"Fig. 14. Attack path model and linkage to system model of seat system"</t>
+  </si>
+  <si>
+    <t>"Fig. 15. Attack path in logical architecture of seat system"</t>
+  </si>
+  <si>
+    <t>"The identified threats as well as the attack-defense trees are visualized to provide a concise and informative view of the analysis."</t>
+  </si>
+  <si>
+    <t>Attack Defense Trees</t>
+  </si>
+  <si>
+    <t>"Figure 3b. Analysis of Requirement 1.1 -what the analysis would look like if the recommended defenses were applied (with a zoomed-in portion showing CAPEC-151)."</t>
+  </si>
+  <si>
+    <t>"Security Attack Scenario enables an analysis of the system’s vulnerable points and the attacks that can exploit these vulnerabilities. The attack scenario can be considered as a sequence of actions dedicated to compromise the system’s integrity, availability, and confidentiality"</t>
+  </si>
+  <si>
+    <t>Misuse Cases, Activity Diagram</t>
+  </si>
+  <si>
+    <t>"Misuse Cases is a security technique that extends Use Cases and allows identifying attackers and their threats to the system of interest. Usually, Misuse Cases are modeled together with Use Cases in the same diagram"</t>
+  </si>
+  <si>
+    <t>"Fig. 4. Flight Status misuse cases"</t>
+  </si>
+  <si>
+    <t>"Fig. 5. Flight Status attack scenario"</t>
+  </si>
+  <si>
+    <t>"In fig. 7 one generated attack tree of the example is shown. Each node of the tree is divided into three section. The first section shows the id of the node. “T” stands for the threat scenario, that needs to be created initially. “AM” stands for an attack method and “AA” stands for Asset Attack, which is the point of attack that a threat agent can initially exploit. In the second section the action that needs to take place to fulfill the node within the attack tree is described. In the third section the affected elements that are involved in the step that is described by the attack tree node are listed."</t>
+  </si>
+  <si>
+    <t>Attack Tree</t>
+  </si>
+  <si>
+    <t>"Vulnerability Cause Graph (VCG) is a directed acyclic graph which is visual representations of vulnerability models, they shows the relation between vulnerabilities and their causes. Figure 8 shows the causes of SQL Injection vulnerability."</t>
+  </si>
+  <si>
+    <t>Vulnerability Cause Graph, Attack Tree, Misuse Cases</t>
+  </si>
+  <si>
+    <t>"Attack Trees or Threat Trees are used to model an attack or threat in a tree like structure. Attack trees are used to analyze the attack surface and recognize the risks and consequences of potential attacks. SQL Injection Attack tree is shown in figure 9."</t>
+  </si>
+  <si>
+    <t>"Misuse Cases are defined as “the inverse of a use case, i.e., a function that the system should not allow [4]. Use case mitigates misuse case and misuse case threatens use case. To define security, we need to understand how someone will misuse the system."</t>
+  </si>
+  <si>
+    <t>"attack-defense tree is a better representation of a system over attack trees because the latter only captures attack scenarios and does not model the interaction between attacks and the defenses that could be put in place to guard against the attacks."</t>
+  </si>
+  <si>
+    <t>"Using attack-defense trees is one way of modeling the sufficiency of mitigations in preventing the success of identified attacks."</t>
+  </si>
+  <si>
+    <t>"In this paper, we propose attack-fault trees (AFTs) as formalism for the combined safety-security analysis. As their name suggests, AFTs overarch both attack trees and fault trees. Fault trees (FTs) are a classical formalism for reliability engineering that is heavily used in industry"</t>
+  </si>
+  <si>
+    <t>Attack Fault Trees, Stochastic Timed Automata</t>
+  </si>
+  <si>
+    <t>"Attack-fault trees (AFTs) model how a top-level (safety or security) goal can be refined into smaller sub-goals, until no further refinement is possible."</t>
+  </si>
+  <si>
+    <t>"Stochastic timed automata (STA) is an extension of timed automata with stochastic semantics. Here, the constraints on the edges and the invariants on the locations are used to enable or force certain transitions at certain times. These constraints and invariants are specified as clocks, which increase linearly over time, but may be reset when a transition is taken."</t>
+  </si>
+  <si>
+    <t>"Attack tree model describes attacks towards any system as a logical function of atomic attacks. A successful security breach due to a cyber attack is called an attack goal. Successive subordinate security breaches are called attack subgoals. The sub-goals can be broken down further to successive events called atomic attacks."</t>
+  </si>
+  <si>
+    <t>Attack Tree, Data Flow Diagram, Petri Net</t>
+  </si>
+  <si>
+    <t>"Next, we lay out the topology as the DFD [14]. Considering the scale and complexity of DFD, two FDs are appropriate for the analysis, which are each connected with one T in Fig.2. According to the features of DFD, Data Flow (DF), Transmission Channel (TC), and Trust Boundary (TB) are shown. DF1, 2, 3, 4 represent the DFs between A and CD, CD and FD, FD and FD, FD and T, respectively. There are two TBs, which are determined by three parts that access users, network, and administrator. TB1 is located between FD and T. TB2 is located between A and CD."</t>
+  </si>
+  <si>
+    <t>"For a better display of the network states, it is necessary to model the modes by Petri net. The modes demonstrate the entities, links, and states graphically and logically."</t>
+  </si>
+  <si>
+    <t>"Among the widely employed frameworks is the AT, which delineates potential attack paths using logical nodes [19]. The AT framework provides a graphical approach to identifying vulnerabilities within a system. It involves decomposing the attacker’s objectives into sub-goals and BASs to describe potential security vulnerabilities in a system, representing all conceivable ways to a system compromise through attacks"</t>
+  </si>
+  <si>
+    <t>Attack Tree, Quantitative Attack Tree, Bayesian Network</t>
+  </si>
+  <si>
+    <t>"Extending the AT framework, the quantitative at tack tree (QAT) integrates probabilities and costs to evaluate security risk [13]. Through the QAT model, security analy sis metrics are derived by assigning attribute values to each BAS,encompassing parameters such as associated cost, skills, resources, and impact of a successful attack"</t>
+  </si>
+  <si>
+    <t>"The proposed approach involves analysing potential attack scenarios to systematically model system security behaviours. The AT modelling creates a hierarchical analysable artefact that serves as a graphical and structural top-down model for system CPS security analysis"</t>
+  </si>
+  <si>
+    <t>"The computation of statistical and stochastic dependencies among BASs is achieved by mapping the attack tree (AT) to a higher statistical model of the Bayesian network (BN) model."</t>
+  </si>
+  <si>
+    <t>"A. Decision tree model: After evaluating and comparing the index performance of several classification and clustering models, this paper uses the decision tree algorithm to realize the model[4,5]."</t>
+  </si>
+  <si>
+    <t>Decision tree model</t>
+  </si>
+  <si>
+    <t>"An attack hierarchy is shown in Figure 2. STRIDE can be used to identify potential threats to any system and to design countermeasures to mitigate those threats. By considering each of these categories, it is possible to build a threat model for a smart traffic control system as shown in Table II."</t>
+  </si>
+  <si>
+    <t>Modelo de jerarquía de ataques STRIDE</t>
+  </si>
+  <si>
+    <t>"MBSEsec is a security-focused MBSE method using SysML to develop a system architecture that highlights security design considerations."</t>
+  </si>
+  <si>
+    <t>MBSEsec</t>
+  </si>
+  <si>
+    <t>"This work explores methods for the use of MBSE approaches to enable secure system design and applies the MBSEsec method to securing the transport layer protocol on MHD vehicles."</t>
+  </si>
+  <si>
+    <t>"The MBSEsec method outlines the activities and steps for designing secure systems with the SysML security profile. The method involves four phases that provide the appropriate techniques and diagrams to be used."</t>
+  </si>
+  <si>
+    <t>"The analysis of a hybrid attack graph based on model checking mainly includes the following process. Firstly, we define a hybrid attack graph model and propose the transformation rules from the hybrid attack graph to the timed automata (TA). Then, we perform model checking according to the defined metric interval temporal logic (MITL). The model checking process includes generating timed automata, determining the security properties MITL, and using TACK to verify the satisfiability of MITL formulations and TA. Finally, the results are analyzed according to the judgment results of the model checking. Fig. 1 presents the framework of the proposed hybrid attack graph analysis method and  model checking process."</t>
+  </si>
+  <si>
+    <t>Model checking/MITL</t>
+  </si>
+  <si>
+    <t>"UML is used for requirement elicitation and to represent the functional and behavioral aspect of a system with the use case, class diagram, and state-chart diagram respectively. There are several extensions proposed to model the feature of security. UMLSec [7] is one of such extension which is model-based security engineering approach to weave security information in system design for analyzing critical security parts of the system."</t>
+  </si>
+  <si>
+    <t>UMLsec</t>
+  </si>
+  <si>
+    <t>"Secure UML: Secure UML is modeling language proposed by Lodderstedt et al. [18] for modeling only access control policies for model driven software development process."</t>
+  </si>
+  <si>
+    <t>SecureUML, UMLsec</t>
+  </si>
+  <si>
+    <t>"UMLsec [19] was proposed in 2002 to facilitate modeling of security scenarios into a system design. UMLsec can be used for model analysis to verify that a particular security requirement is satisfied or not. It lacks capabilities for modeling security problems."</t>
+  </si>
+  <si>
+    <t>"The developed approach for modeling attack paths is based on the RAAMLspecification and defines a profile and a library as an extension of the RAAML-defined core and general profiles and libraries"</t>
+  </si>
+  <si>
+    <t>RAAML</t>
+  </si>
+  <si>
+    <t>"The attack path modeling approach follows the RAAML principle of a heavily used library approach with a light profile support "</t>
+  </si>
+  <si>
+    <t>"MODEL-BASED ARCHITECTURAL ANALYSIS (MBAA): The purpose of analyzing the architecture is to determine if the system is resilient enough to perform a given mission. We start at the architecture level because a lot can be analyzed just from knowing what types of components are in the system, how they are connected, what type of information flows between them, and their exposure to threats from outside the system’s trusted boundary."</t>
+  </si>
+  <si>
+    <t>MBAA</t>
+  </si>
+  <si>
+    <t>pág- 1</t>
+  </si>
+  <si>
+    <t>"in this paper, we introduce how Model-based System Engineering (MBSE) could be leveraged in order to tackle security issues while recreating legacy software systems."</t>
+  </si>
+  <si>
+    <t>"This section presents an approach for identifying security issues with MBSE which includes guidelines on how and when to apply security following techniques."</t>
+  </si>
+  <si>
+    <t>pág. 1-2</t>
+  </si>
+  <si>
+    <t>"the general principles of model-based system development are presented."</t>
+  </si>
+  <si>
+    <t>"Many organizations direct their application security efforts on automated detective solutions such as application scans, penetration testing, web application firewalls and patch management rather than preventing the defects from occurring in the first place i.e. during development of web application. The dominating idea, ‘Secure Software Engineering’ saves time as well as cost for mitigating vulnerabilities. Keeping in line with the context of security in software development, this paper focused on mitigating SQL Injection vulnerability in SDLC."</t>
+  </si>
+  <si>
+    <t>Secure Software Engineering</t>
+  </si>
+  <si>
+    <t>"The zoomed in portion shows that to combat against identity spoofing—CAPEC-151 [14]—on the RC_receiver, a defense profile made up of 8 NIST 800-53 [15] security controls should be applied."</t>
+  </si>
+  <si>
+    <t>NIST, CAPEC</t>
+  </si>
+  <si>
+    <t>"Technically, our approach is based on (SMC) [20], [21], a state-of-the-art method for stochastic analysis. SMC has been deployed in a wide number of areas, communication theory [22], systems biology [23], and many more [24]. Key feature of SMCtechnique is its compositionality, allowing one to build large models by composing smaller ones. In this paper, we exploit the compositional SMC approach and translate each element (i.e., leaf or gate) of an AFT into a stochastic timed automaton (STA, [25])."</t>
+  </si>
+  <si>
+    <t>Statistical Model Checking (SMC)</t>
+  </si>
+  <si>
+    <t>"In addition, it introduces the security analysis method of STRIDE to build up the Attack tree model."</t>
+  </si>
+  <si>
+    <t>"Building up the Attack tree model [18] for the Place and Transition in Petri net by introducing the security analysis method of STRIDE."</t>
+  </si>
+  <si>
+    <t>"For further exploration of the development of an attack tree using a document-based approach or by leveraging model-based systems engineering (MBSE) models"</t>
+  </si>
+  <si>
+    <t>"We adopt the STRIDE threat modeling technique to identify threats and vulnerabilities."</t>
+  </si>
+  <si>
+    <t>"In this section, we are going to provide a security analysis and build a threat model for a smart traffic control system. We start by listing the essential assets for the smart traffic control system, then we will identify the possible entry points which could be exploited by attackers to access those assets, then we will demonstrate possible threats and attacks and design a threat model using the STRIDE approach."</t>
+  </si>
+  <si>
+    <t>"To identify the threats for the smart traffic control system in a further systematic manner, we are going to use STRIDE which is an acronym for a threat modeling technique developed By Microsoft as a part of the Software Development Lifecycle SDLC."</t>
+  </si>
+  <si>
+    <t>"Once accessed, either via a physical connection to the J1939 port or through wireless connections like telematics, an attacker can read J1939 data, send messages, and send commands to the ECUs."</t>
+  </si>
+  <si>
+    <t>DoS, Tampering, Information Disclosure</t>
+  </si>
+  <si>
+    <t>"Attacks have been discovered at multiple layers of network communication, primarily the application layer, network management layer, and data-link layer. Chatterjee et al., [28] validate five different cases in which shortcomings of the J1939 data-link layer can be exploited. The five attacks are detailed below: 1) Request Overload Attack 2) Connection Exhaustion Attack 3) BAM Block Attack 4) Malicious CTS Attack 5) Memory Leak Attack"</t>
+  </si>
+  <si>
+    <t>pág. 4.</t>
+  </si>
+  <si>
+    <t>"To construct the hybrid attack graph of the smart home system, we assume that the attacker can use five attack methods against the smart home system: (1) An attacker can connect to the home's internal LAN to obtain the IP address of the home camera. So the attacker can easily get into the system if the user sets a login page with a weak password. In contrast, the user can set the login page to use a strong password. In that case, the attacker can enter the surveillance camera operation interface by brute force cracking to achieve the target of adjusting the camera angle. (2) The attacker can enter the home internal LAN by connecting the network interface on the smart light and then obtain the network transmission data. On this basis, the attacker can achieve the target of triggering the smoke alarm by tampering with the detection value of the smoke alarm. (3) The attacker can enter the home internal LAN by connecting the network port on the smart light and then obtain the network transmission data. Further, he/she enters the camera operation page to realize the attack target by adjusting the camera angle. (4) The attacker can enter the home internal LAN by connecting the network interface on the smart light to obtain network transmission data. Then he/she obtains the control authority of the smart home speaker and realizes the attack target of recording through the smart speaker. (5) An attacker can enter the home internal LAN by connecting the network interface on the smart light to obtain network transmission data. Then he/she obtains the control authority of the smart home speaker and realizes the attack target of controlling other home devices through the authority of the smart speaker."</t>
+  </si>
+  <si>
+    <t>Fuerza bruta, Intercepción de datos, Acceso no autorizado</t>
+  </si>
+  <si>
+    <t>"major security objectives of smart systems [2] include integrity (ensuring and maintaining the completeness and accuracy of resources by restraining intentional or unintentional modification), confidentiality (authorized restrictions on proprietary information access and disclosure), availability (ensuring system execution in fault-free manner to provide expected services for specified time t), privacy, non repudiation (controlling the deliberate repudiation), auditability (consistent monitoring of actions of users)"</t>
+  </si>
+  <si>
+    <t>DoS, Repudiation, Intercepción de datos, Acceso no autorizado</t>
+  </si>
+  <si>
+    <t>"Fig: 02. Use case for store data application"</t>
+  </si>
+  <si>
+    <t>Manipulación de datos</t>
+  </si>
+  <si>
+    <t>"Fig: 03. Mitigation Use case for store data application including security pattern solution"</t>
+  </si>
+  <si>
+    <t>Fig.9.  Authorization Diagram for Faculty Member 
+TABLE VII.      AUTHORIZATION TEMPLATE</t>
+  </si>
+  <si>
+    <t>Acceso no autorizado, Manipulación</t>
+  </si>
+  <si>
+    <t>"The emerging network of (safety-critical) aircraft systems not only facilitates informa tion exchange but also introduces the potential for malicious interaction, thereby exposing these systems to cyber attacks and posing substantial security risks."</t>
+  </si>
+  <si>
+    <t>Manipulación</t>
+  </si>
+  <si>
+    <t>“1.1 The UAV shall be resilient to loss of ability to perform reconnaissance of designated civilian habitat” and “1.2 The UAV shall be resilient to maliciously commanded improper reconnaissance.”</t>
+  </si>
+  <si>
+    <t>DoS, Manipulación</t>
+  </si>
+  <si>
+    <t>the “Incoming Data Processing” microservice shall ensure the accuracy and consistency of supplier data during transfer.</t>
+  </si>
+  <si>
+    <t>Manipulación, DoS, Tampering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the “Incoming Data Processing” microservice shall ensure continuous availability to the legitimate users, whenever they require it. </t>
+  </si>
+  <si>
+    <t>"In Fig. 1 the generation process is presented. The approach presented here is currently limited to data manipulation and denial of service attacks with respect to cyber-physical systems. The process is divided into 5 main steps, which are described in detail below."</t>
+  </si>
+  <si>
+    <t>Manipulación de datos, DoS</t>
+  </si>
+  <si>
+    <t>"SQL injection or insertion is the most widespread and brutal attack having high risk rating"</t>
+  </si>
+  <si>
+    <t>SQL Injection</t>
+  </si>
+  <si>
+    <t>"Safety and security are heavily intertwined: measures that increase safety often decrease security and vice versa: Imple menting access policies may deter adversaries, but act as a hindrance in case of emergency operations; a non encrypted industrial communication is a simpler design choice, however it can be exploited by attackers to spoof the network. Thus, given their mutual dependence, safety and security should be considered in a combination, so that tradeoffs can be made."</t>
+  </si>
+  <si>
+    <t>Spoofing</t>
+  </si>
+  <si>
+    <t>"In this step, STRIDE (Spoofing, Tampering, Repudiation, Information disclosure, Denial of service, Elevation of privilege) is quoted to assist in analyzing the vulnerability of elements in FCSNS."</t>
+  </si>
+  <si>
+    <t>Spoofing, Tampering, Repudiation, Information disclosure, Denial of service, Elevation of priviledge</t>
+  </si>
+  <si>
+    <t>"The advancement in the design and architecture of CPS technology, which integrates computational and physical pro cesses, has opened up increased attack vectors that are susceptible to a wide range of cyber threats due to their com plex connectivity and distributed nature of the CPS network structure [1]. CPS environments are susceptible and vulnera ble to random hardware failures, malfunctions, cyber-attacks, and other vulnerabilities, leading to potential consequences and liabilities [15], [16], [17]. As a result, security-induced malfunctions in CPS can pose threats to human life, harm the environment, and cause financial or reputational losses."</t>
+  </si>
+  <si>
+    <t>Denial of Service, Daño ciberfísico</t>
+  </si>
+  <si>
+    <t>"Mark according to the category to which the feature belongs, and the labels include: normal, scan, synflood, ackflood, UDP flood. take samples with roughly the same amount of data in each category to form a training set, and then use the decision tree model for training."</t>
+  </si>
+  <si>
+    <t>Denial of Service, Escaneo de puertos</t>
+  </si>
+  <si>
+    <t>"One common approach to threat modeling is the STRIDE which was developed by Microsoft and used to identify six categories of threats. STRIDE stands for Spoofing, Tampering, Repudiation, Information Disclosure, Denial of Service, and Elevation of Privileges. STRIDE helps to identify vulnerabilities and threats by dividing them into these categories."</t>
+  </si>
+  <si>
+    <t>"STRIDE Stands for six categories of threats as follows: Spoofing of Identity, Tampering, Repudiation, Information Disclosure, Denial of Service, and Elevation of privileges. STRIDE helps to identify and prioritize systems security vulnerabilities and threats."</t>
+  </si>
+  <si>
+    <t>"This section will present an overview of the SAE J1939 network as implemented in medium and heavy-duty trucks (MHD). MHD vehicle mechanical operations, as well as data record ing and display, are primarily controlled by Electronic Control Units (ECUs). These ECUs form networks within the vehicle to communicate information and commands to other entities via a bus topology. The ECUs within these vehicles utilize J1939 which is an application layer communication protocol built on top of CAN."</t>
+  </si>
+  <si>
+    <t>Sistemas vehiculares</t>
+  </si>
+  <si>
+    <t>"Attack graph is an essential tool for the security assessment of industrial Internet systems."</t>
+  </si>
+  <si>
+    <t>Sistemas de Internet Industrial</t>
+  </si>
+  <si>
+    <t>"Before the emergence of smart systems majority of security threats are related to information leakage and the denial of service to challenge physical security risk. Although, with the advent of smart systems supported with IOT and cyber-physical systems [1], there is a need of dependable solutions for designing a smart environment that can support dynamic system, multi-profile platforms and secure device interactions within the cyber and physical environment."</t>
+  </si>
+  <si>
+    <t>Sistemas IoT</t>
+  </si>
+  <si>
+    <t>"ROLE Based Access Control (RBAC) pattern was designed for Library circulation system using aspect oriented programming."</t>
+  </si>
+  <si>
+    <t>Sistemas de Información Empresariales</t>
+  </si>
+  <si>
+    <t>"They mapped the UML deployment diagram notations with the security pattern elements and designed the security architecture of the healthcare information system using solution provided by security patterns."</t>
+  </si>
+  <si>
+    <t>"The methodology has been explained through a library management system case study. However, owing to space constraints, a limited view has been presented in this paper."</t>
+  </si>
+  <si>
+    <t>"A. Security Concepts for Airworthiness Security: The objective of the certification specification CS-25.1319 [1] is to protect the aircraft and aircraft systems from IUEI."</t>
+  </si>
+  <si>
+    <t>Aircraft systems, Avionics</t>
+  </si>
+  <si>
+    <t>"The HawkeyeUAV system can operate in either manual or autonomous flight mode. In manual flight mode, the responsibility of navigation is deferred to a remote pilot component which communicates with the UAV system through a radio-frequency channel."</t>
+  </si>
+  <si>
+    <t>Legacy Software Systems</t>
+  </si>
+  <si>
+    <t>"To demonstrate our MBSE security approach usage for rebuilding legacy systems, we selected the real-world Flight Status system which collects data from various sources"</t>
+  </si>
+  <si>
+    <t>"Modular Vehicle Systems (MVS) is a trending topic that are being researched in several Projects, in which the vehicles can be flexibly reconfigured by the user or fleet operator using platform modules for corresponding applications. In addition to high flexibility, these systems are characterized by a high degree of automation."</t>
+  </si>
+  <si>
+    <t>Sistemas de Vehículos Modulares</t>
+  </si>
+  <si>
+    <t>"The core cause behind increase of SQLI is “Unsecure Software Engineering”. Developers think Security as an obstacle in the development of web application."</t>
+  </si>
+  <si>
+    <t>"web applications can contain yet vulnerabilities. Nevertheless, the dominating idea, i.e. Secure Software Engineering, offers reduction in future expenditures as well as more in-depth defense"</t>
+  </si>
+  <si>
+    <t>"Our work is based on two publications on airworthiness security process and design methods: RTCA DO-326A [4] and DO-356A [5].  The two paired together provide guidance to assess and improve the security of an aircraft, but the guidance can also be used on other large and complex systems of systems."</t>
+  </si>
+  <si>
+    <t>Sistemas de Aeronavegabilidad</t>
+  </si>
+  <si>
+    <t>"Cyber physical systems, like power plants, medical devices and data centers have to meet high standards, both in terms of safety (i.e. absence of unintentional failures) and securityv(i.e. no disruptions due to malicious attacks)."</t>
+  </si>
+  <si>
+    <t>Sistemas Ciber-Físicos</t>
+  </si>
+  <si>
+    <t>"The top event (see figure 18) Pollution can occur via spillage of toxic substance only if either there is an attack and then a pipeline failure (modelledwithaPAND gate) or a pipeline failure followed by a sequentially an accidental protection failure (modelledwithaSANDgate)."</t>
+  </si>
+  <si>
+    <t>"However and to the best of our knowledge, there is still little attention given to the security analysis of Forwarding and Control planes Separation Network Structure (FCSNS), as well as SDN. Reference [15] and [16] analyze the security of SDN architecture."</t>
+  </si>
+  <si>
+    <t>Redes definidas por software (SDN)</t>
+  </si>
+  <si>
+    <t>"However and to the best of our knowledge, there is still little attention given to the security analysis of Forwarding and Control planes Separation Network Structure (FCSNS), as well as SDN. Reference [15] and [16] analyze the security of SDN architecture. Six vulnerabilities in SDN control platforms were listed in [15]."</t>
+  </si>
+  <si>
+    <t>"The application of this framework was demonstrated using an intelligent glucose monitoring and insulin administration system (IGMIAS)."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intelligent Glucose Monitoring and Insulin Administration System </t>
+  </si>
+  <si>
+    <t>"To demonstrate the implementation of the proposed frame work, we utilised a high-level architectural description of a smart IGMIAS as outlined in [39]. The system utilises in telligent sensors to monitor blood glucose levels in diabetic patients. It integrates an insulin pump to continuously ad minister insulin, effectively managing blood glucose levels and preventing severe hypoglycaemia by minimising fluctu ations"</t>
+  </si>
+  <si>
+    <t>"We deploy each model to an offline environment, detect real-time traffic data of devices, and use C&amp;C tools to send traffic attack instructions to abnormal traffic programs in the devices. We test whether they can recognize traffic of types ackFlood, udpFlood, synFlood, scan, and normal normally normally."</t>
+  </si>
+  <si>
+    <t>Sistemas de control de tráfico</t>
+  </si>
+  <si>
+    <t>"An example of a smart city’s service is a smart traffic control system [1]. A system designed to improve the city’s overall transportation system including traffic efficiency, safety, and traffic management. Such a system uses sensors, cameras, and network connections to analyze traffic flow and conditions in real-time. Based on traffic analysis, the system can adjust traffic signals and optimize routing to resolve traffic congestion [2]."</t>
+  </si>
+  <si>
+    <t>"In this paper, we use a threat model-based approach to perform a systematic security analysis of smart city traffic control systems."</t>
+  </si>
+  <si>
+    <t>"This is the case for new systems in design and a possible challenge for practitioners with limited expertise on the system or similar systems. If a full system architecture is present, more security require ments are likely to be available or generated, but systems in earlier phases of system design will have more unknowns in implementation and more challenges to compiling a set of security requirements to begin the MBSEsec method."</t>
+  </si>
+  <si>
+    <t>Dependencia de expertos, Conbertura incompleta</t>
+  </si>
+  <si>
+    <t>•	Misuse case: Informal approach and lack of behavioural aspect
+•	Abuse case: Informal approach, missing behavioral aspect
+•	Fault tree: Bulky, Unable to model sequential dependency
+•	Attack tree: Lack of standard techniques to build, simulate, and analyze attack trees
+•	Privilege tree: Lack of standard technique of analysis, bulky
+•	Petri net: Complex for large systems, not scalable
+•	Bayesian network: Usefulness depends on prior knowledge reliability, process of network discovery is an NP-hard task</t>
+  </si>
+  <si>
+    <t>Alta complejidad, Dependencia de expertos, Falta de estandarización</t>
+  </si>
+  <si>
+    <t>"Development of secure software system is a challenging task. It is the responsibility of the software designer or architect to define security requirements along with the function requirements of the system to accommodate the developers. Architectural diagrams for functional and non-functional requirements should be defined in such a way that it can accommodate the secure development along with proper functionality. To achieve these goals, the architect must consider a set of constraints, including technical limitations and functional goals of the system. The solution presented usually based on the architect’s experience and knowledge. Bearing in mind that most of programmers are very good in development but they lack expertise when it comes to security implementation. Guide developers about security implementation and location of security mechanisms are crucial tasks which will reduce overall cost, time and effort in software development process. Due to unavailability of a common method to model the security, non-security expert programmers and developers face problems to understand the security constraints."</t>
+  </si>
+  <si>
+    <t>Falta de estandarización, Dependencia de expertos</t>
+  </si>
+  <si>
+    <t>"The conventional belief was that cyberattacks on critical infrastructures designed as embedded systems are of no concern because they were seldom connected to the network from which these attacks were enabled. However, attackers have learned to bridge air gaps – even the most remote and physically guarded infrastructures can be attacked [1]. In short, embedded systems are now subject to cyberattacks, either as the end goal of the cyber assailant or as a means to a greater end."</t>
+  </si>
+  <si>
+    <t>"In addition, it is expected that the vehicle modules will be provided on a rental basis and thus be in use almost 24/7. This creates special challenges in the context of cybersecurity, since a large number of module combinations must be considered and evaluated in advance."</t>
+  </si>
+  <si>
+    <t>Alta complejidad, Falta de escalabilidad</t>
+  </si>
+  <si>
+    <t>"More importantly, security of a system is constantly evolving – as better control measures are put in place, more sophisticated attacks are implemented. Therefore, modeling only attacks without considering the defenses in place is very limiting."</t>
+  </si>
+  <si>
+    <t>Cobertura incompleta</t>
+  </si>
+  <si>
+    <t>"Safety and security are heavily intertwined: measures that increase safety often decrease security and vice versa: Imple menting access policies may deter adversaries, but act as a hindrance in case of emergency operations;"</t>
+  </si>
+  <si>
+    <t>Trade-Offs</t>
+  </si>
+  <si>
+    <t>"The limitations of AT models and their extensions stem from the assumption that the probabilities of BASs are known precisely or can be easily deduced [19]. Obtaining accurate parameter values for BASs is challenging due to the difficulty in obtaining statistics on attacker capabilities and the rapidly changing nature of security threats [11], [21]. This under scores the need for methods to handle uncertain parameter values and provide at least an approximate estimation of security events. Additionally, the AT model struggles to effectively model real-world complexities where BASs share stochastic and statistical dependencies, making realtime risk evaluation challenging when using a Tree-based model [20]."</t>
+  </si>
+  <si>
+    <t>Cobertura incompleta, Dependencia de expertos, Alta complejidad</t>
+  </si>
+  <si>
+    <t>"In practical terms, obtaining precise knowledge of BAS parameters such as attacker capabilities, cost, and resources are seldom feasible and are widely subjective [19], [22].Reliable statistics can be challenging to obtain, and historical data often lacks relevance due to the rapidly evolving threat landscape [11], [16], [19], [21]. This presents a challenge for quantitative security analysis, as accurate parameter values are important for generating meaningful results that can be used for CPS security standardisation."</t>
+  </si>
+  <si>
+    <t>"This article introduces a comprehensive approach to quantitative cybersecurity analysis in CPS. The approach proposes a novel framework integrating expert elicitation, fuzzy logic, AT, and BN to model and quantify security risks based on CPS design architecture."</t>
+  </si>
+  <si>
+    <t>"A smart city’s traffic control system utilizes Information and Communication Technologies (ICT) to enhance its transportation system as a part of all integral smart systems in the city. The advanced technologies in smart cities can bring solutions to various issues that exist in traditional cities around the world, however, those technologies can be the source of other issues, especially security issues [4]. While the ICT technologies such as IoT and Cloud computing can help build smart cities system, [18] Smart cities rely on ICT technologies such as IoT and Cloud technologies which increase the attack surface."</t>
+  </si>
+  <si>
+    <t>Alta complejidad, Falta de estandarización, Aumento de la superficie de ataque, Dependencia de terceros.</t>
+  </si>
+  <si>
+    <t>"3.2.1. The TRADES design diagram: The design diagram is the main representation of TRADES. It is used for creating, updating and communicating the TRADES information model, and specifically the threat analysis with respect to the system composition. Its notation is overviewed in Table 1 and discussed below. System components are used as containers. This design illustrates that components are hierarchical structures, reflecting the responsibility scope. Specifically, the responsibility of a system designer is for the elements that fall within the boundary line of the system’s element box- like representation."</t>
+  </si>
+  <si>
+    <t>TRADES Design Diagram</t>
+  </si>
+  <si>
+    <t>"4.2.4. Modeling of the system For the item definition of the system we used the block definition diagram (bdd) of SysML. The blocks, their hierarchy and multiplicities (e.g. exactly one module consists of at least one cell) are defined based on the use case description and requirements (cf. Fig. 8 [Top]). Fur thermore, all input and output ports are defined as known so far. This item definition is compliant to ISO 26262 and subject to further safety and security analyses."</t>
+  </si>
+  <si>
+    <t>Diagrama de Definición de Bloques, Data Flow Diagram</t>
+  </si>
+  <si>
+    <t>"Perform security analysis. In this context, Security Engineering follows the initial definition of a safety pattern to identify potential security threats and vulnerabilities in the design, and to assess the risks in order to find appropriate countermeasures and apply corresponding security patterns. In this example, we use the threat modeling methodology [32], in which a system is modeled in a Data Flow Dia gram (DFD). When modeling the functional blocks from the safety pattern (cf. Fig. 4) in a DFD, a few transitions and extrapolations occur."</t>
+  </si>
+  <si>
+    <t>"Fig. 2 shows the class diagram that adds security controls of Table 1 . Each one represents a specification (blue boxes). However, effective realizations of these controls are not modeled in the UML class diagram; they may be subject to certain changes and/or adaptations (new security solutions, deletions, modifications of realization, for instance), verifications (formal and empirical, for instance) and reuse (in the same domain or across domains, for instance) while the structure of the main software architecture can be maintained. Fig. 3 shows the class diagram that adds new components to realize the security controls of Table 1."</t>
+  </si>
+  <si>
+    <t>Diagrama de Clases con Extensión de Seguridad</t>
+  </si>
+  <si>
+    <t>"To do so, SoCo supports engineers in identifying and integrating appropriate technical controls in sequence diagrams during the design phase."</t>
+  </si>
+  <si>
+    <t>Diagramas de secuencia con extensiones de seguridad</t>
+  </si>
+  <si>
+    <t>"To tackle these problems, this paper proposes SoCo, a semi-automated approach to support engineers, during the design phase of a SDLC, in integrating priv&amp;sec controls within sequence diagrams of software design for processing personal data securely and ensuring GDPR compliance."</t>
+  </si>
+  <si>
+    <t>"The selected priv&amp;sec controls are injected automatically within the sequence diagrams of software design representing data flows violating the GDPR."</t>
+  </si>
+  <si>
+    <t>"System modeling leverages the MACM formalism introduced in (Rak, 2017), enabling to describe the high-level architecture of an application in terms of a graph, whose nodes represent the main components of the application, belonging to a set of pre-defined types with specific properties, and whose edges represent the interconnections of the components. (Fig. 2)"</t>
+  </si>
+  <si>
+    <t>Multi-purpose Application Composition Model (MACM)</t>
+  </si>
+  <si>
+    <t>"This paper focuses on the creation of the security knowledge artifacts and their main elements. We illustrate this description with an example that shows how a security knowledge artifact,named Domain Security Metamodel (DSM),is created usingWeb Service Security specification as basis."</t>
+  </si>
+  <si>
+    <t>Domain Security Metamodel (DSM)</t>
+  </si>
+  <si>
+    <t>pág. 13</t>
+  </si>
+  <si>
+    <t>"This section presents the creation of a Domain Security Metamodel (DSM),the artifact responsible for representing the security knowledge of a specific domain to be used in the SEP."</t>
+  </si>
+  <si>
+    <t>"This artifact, called Domain Secu rity Metamodel (DSM), is, as its name suggests, domain-specific and contains information about all security aspects that are relevant in a specific domain (e.g. embedded systems, web services, etc.)."</t>
+  </si>
+  <si>
+    <t>"TRADES is a model-based engineering methodology for supporting the design and assessment of systems from a security perspective. We emphasize that model-based engineering refers to the reliance on digital information models for performing engineering tasks. The digital in formation models are the key artifacts, supporting rigorous recording, construction, communication and analysis of the structured data (which is contained within them). The following subsections describe the TRADES design, while providing justification for the design by relating it to the SSDA domain concepts and context of use."</t>
+  </si>
+  <si>
+    <t>TRADES, MBSE</t>
+  </si>
+  <si>
+    <t>"Furthermore, we extended the application of the methodology on the battery man agement system case study regarding support of pattern engineering by further use case scenarios and emphasizing Model-based Systems En gineering (MBSE)."</t>
+  </si>
+  <si>
+    <t>MBSE, ISO 26262</t>
+  </si>
+  <si>
+    <t>"ISO 26262 (“Road vehicles- Functional safety”) [4] is an automotive domain-specific safety standard. It provides a structured and generic approach for the complete safety life cycle of an automotive E/E system including design, development, production, service processes, and decommissioning. ISO 26262 recommends requirements and techniques for system, software, and hardware design to achieve functional safety for E/E systems."</t>
+  </si>
+  <si>
+    <t>"Model-Based Systems Engineering (MBSE) is an efficient approach to specify, design and analsze complex systems. Estefan et. al [22] provide an overview of MBSE methodologies and cover a collection of related processes, methods, and tools used to support the discipline of systems engineering and the role of the system modeling language SysML in that context."</t>
+  </si>
+  <si>
+    <t>"In our work, we propose a model-driven engineering (MDE) methodological approach associated with a pattern-based approach to support the development of secure software systems."</t>
+  </si>
+  <si>
+    <t>"In this paper, we present a model-based approach for en- gineering secure systems that uses patterns to represent secu- rity solutions and knowledge, which fosters reuse. This work is conducted within the context of a model-based security and dependability research project, and our collaboration with security-critical system suppliers suggested a need for this work."</t>
+  </si>
+  <si>
+    <t>"We use MDE ( Atkinson and Kühne, 2003 ) abstraction mechanisms to define and handle security patterns through a metamodel that unifies those concepts. Moreover, we use MDE transformation mechanisms ( France and Rumpe, 2007; Selic, 2003 ) that can adapt and generate different representations, where patterns are clearly related to domain models."</t>
+  </si>
+  <si>
+    <t>"2.1. GDPR compliance Achieving compliance with any data protection law is an organizational-wide effort. This task typically involves different stakeholders, such as data users, DP experts, and engineers, when compliance relates to implementing changes to software systems. Regardless of the organization, one of the first steps towards GDPR compliance is conducting a data mapping exercise to create a data inventory"</t>
+  </si>
+  <si>
+    <t>GDPR, Privacy-by-design</t>
+  </si>
+  <si>
+    <t>"the tool and approach help advance the knowledge in the discipline of secure software engineering and privacy-by-design. They accomplish this by providing practical artifacts and novel tech niques that engineers can use to select priv&amp;sec effectively controls to ensure GDPR compliance and efficiently apply them to design artifacts of software systems. Ultimately, the tool and approach facilitate the evolution of such systems to achieve GDPR compliance."</t>
+  </si>
+  <si>
+    <t>"to security-by-design principles, our development methodology takes security into account from the planning stage, by providing support for threat modeling and countermeasure selection."</t>
+  </si>
+  <si>
+    <t>Security-by-design, SSDE</t>
+  </si>
+  <si>
+    <t>"we presented a Se curity SLA-based Security-by-Design Development methodology (SSDE methodology for short) aimed to support developers during the phases of threat modeling, risk analysis, security design, and static security assessment, through semi-automated techniques. The SSDE methodol ogy presents a major limitation, i.e., it is only focused on development (from design to coding), not considering any dynamic security testing activities."</t>
+  </si>
+  <si>
+    <t>"we have developed a Security Engineering Process (SEP) (Ruiz et al., 2013b) for engineering secure systems. The SEP is composed of a set of sub-processes that focuses on the ability to represent secu rity knowledge in the form of flexible and reusable artifacts and on the computer-assisted use of such artifacts for creat ing secure systems.The SEP’s main focus is to help developers and engineers in creating secure systems by using security knowledge provided by experts."</t>
+  </si>
+  <si>
+    <t>Security Engineering Process (SEP)</t>
+  </si>
+  <si>
+    <t>"we presented the Security Engineering Process from the point of view of the system engineers (Ruiz et al., 2015) with ex amples of how to create a secure system using our solution."</t>
+  </si>
+  <si>
+    <t>"Fig. 2. Ship missile defense system security design. This figure showcases the use of the design diagram within the context of applying the TRADES methodology and how the design may evolve throughout the development life cycle: (a) Allocation of threats to the system in its black-box representation; (b) System composition is identified; (c) the RADAR component design is further detailed with a subcomponent and a security control; (d) the system design is further detailed and assessed  with respect to allocated threats."</t>
+  </si>
+  <si>
+    <t>Denegación de Servicio, Manipulación de datos</t>
+  </si>
+  <si>
+    <t>"Fig. 3. The risk matrix view for the SMDS system."</t>
+  </si>
+  <si>
+    <t>"Some security architecture strategy might impair, for example, the communication time between components, causing a command to arrive late."</t>
+  </si>
+  <si>
+    <t>Acceso no autorizado, Inyección de datos</t>
+  </si>
+  <si>
+    <t>"We selected the Monitor- Actuator Pattern [16] (cf. Fig. 4 [Right]) which provides heterogeneous redundancy. This pattern adds to the architecture a monitoring channel that detects possible faults and triggers the primary channel to enter its fail-safe state."</t>
+  </si>
+  <si>
+    <t>"Threat: Attack CAN bus through in-car CI. Comment: The communications from the external CI to the CAN bus is responsible for establishing and maintaining communications for charging control. An attacker can use the in-car CI as an entry point by compromising the external CI or tampering with the communications between the interfaces to inject malicious content into the CAN bus."</t>
+  </si>
+  <si>
+    <t>pág. 19</t>
+  </si>
+  <si>
+    <t>"he data to be remotely read out (measurement data and compulsory relevant log for meters) is protected against manipulation with the help of digital signatures."</t>
+  </si>
+  <si>
+    <t>Manipulación, Acceso no autorizado, Intercepción</t>
+  </si>
+  <si>
+    <t>pág. 20</t>
+  </si>
+  <si>
+    <t>"The gateway verifies the probe and responds with its own connection initiation to the remote entity if the authenticity of the probe is satisfied. If the probe is found to be unauthentic, the gateway simply drops the probe without any response."</t>
+  </si>
+  <si>
+    <t>"All the communication that occurs afterwards is encrypted using the algorithms and keys, etc., negotiated during the handshake. Thus, the data transmission occurs with authentic entities and is confidential."</t>
+  </si>
+  <si>
+    <t>"A personal data breach can occur when an organization suffers a security incident that leads to any accidental or unlawful destruction, loss, alteration, disclosure of, ✩ Editor: Patricia Lago. ∗ Corresponding author. or access to personal data (DPC Ireland, 2019). This demonstrates that, although security and privacy are intertwined, they are both required to comply with data protection (Herzog, 2016)."</t>
+  </si>
+  <si>
+    <t>Violación de privacidad, Manipulación, Repudio</t>
+  </si>
+  <si>
+    <t>"the SIS does not log enough data to prove why and who changed the grade to support a grade rectification. This violates the Accuracy DPP, which claims that ‘‘every reasonable step must be taken to ensure that personal data that are inaccurate ... are erased or rectified without delay’’"</t>
+  </si>
+  <si>
+    <t>"Let us suppose the SIS fails to provide students with a clear consent mechanism and instead assumes their implicit consent for reusing their information for non-directly teaching related activitieslike automatically being added to marketing communications when registering to a course (as illustrated in Fig. 2)."</t>
+  </si>
+  <si>
+    <t>Table 4
+Examples of threats from the catalogue.</t>
+  </si>
+  <si>
+    <t>Injection Flaws, Online Guessing, Unauthorized Entry, Spoofing External IPv6, Container Escape</t>
+  </si>
+  <si>
+    <t>Table 5
+Extract of threats-assets associations for the case study application.</t>
+  </si>
+  <si>
+    <t>Table 6
+Extract of final threats analysis with the associated security controls.</t>
+  </si>
+  <si>
+    <t>pág. 15</t>
+  </si>
+  <si>
+    <t>Fig. 10– Web Services Property Sub-model.</t>
+  </si>
+  <si>
+    <t>Intercepción, Manipulación, Acceso no autorizado</t>
+  </si>
+  <si>
+    <t>pág. 16</t>
+  </si>
+  <si>
+    <t>Fig. 11– Web Services Requirement Sub-model.</t>
+  </si>
+  <si>
+    <t>pág. 17</t>
+  </si>
+  <si>
+    <t>Fig.12–WebServicesThreatSub-model.</t>
+  </si>
+  <si>
+    <t>Fig.13–WebServicesAssuranceSub-model.</t>
+  </si>
+  <si>
+    <t>"We discuss a case study of a Ship Missile Defense System (SMDS) design. This case study, which is based on several real-life applications, overviews a typical application of the TRADES methodology and pro vides concretization of the design and risk matrix representations. Considering the SMDS as a black-box (e.g., in an early stage of the system development, when only high-level description of the system exists, such as in the system requirements definition phase)"</t>
+  </si>
+  <si>
+    <t>Ship Missile Defense System, Intellectual Property Governance</t>
+  </si>
+  <si>
+    <t>"The case study is a new, further elaboration of a previously reported technical Intellectual Property (IP) governance case study [43]. IP is explicitly identified as a stakeholder security interest [1]. As depicted in the previous publication, an organization was interested in establishing an IP governance process, and part of this process was to provide design guidelines to system development efforts. The subprocess of providing such guidelines is performed with respect to a preliminary system design; and it relies on an information repository of reverse engineering (RE) techniques as well on IP protection requirements."</t>
+  </si>
+  <si>
+    <t>Sistemas Automotrices</t>
+  </si>
+  <si>
+    <t>"Our automotive use case example of a connected electrified hybrid powertrain is a combination of one or more electric motor(s) and a conventional internal combustion engine, which is currently the most common variant of hybrid powertrains. The variety of powertrain configuration options increases the complexity of the powertrain itself as well as the required control systems, which include software functions and electronic control units. With the integration of connectivity features, further novel vehicle functionalities and new business models can be discovered."</t>
+  </si>
+  <si>
+    <t>"an empirical evaluation of the proposed approach is presented through a practical application to a use case in the metrology domain with strong security requirements, which is followed by a description of a survey performed among domain experts to better understand their perceptions regarding our approach."</t>
+  </si>
+  <si>
+    <t>Sistemas de Metrología, Sistema Bibliotecario</t>
+  </si>
+  <si>
+    <t>"To provide a concrete example, we use smart meter sys- tems. In these systems, there are a number of subsystems working together to communicate and exchange the up to date sensing and measurement of energy consumed with the smart grid. Within these large systems, we focus only on a smart meter gateway as the communication unit of modern smart meters."</t>
+  </si>
+  <si>
+    <t>"The example is based on an OWASP example of a college library website ( OWASP, 2017a ). Fig. 1 shows the overall architecture description of the web application. It consists of a client, a web server and a database server software components. The website provides online services for searching for and for requesting books. The users are students, college staff and librarians. Staff and students will be able to log in and search for books, and staff members can request books. Librarians will be able to log in, add books, add users, and search for books. We use UML class diagram to describe the high level architecture model of the web application, where software components are represented by classes, and relationships between these components are represented by associations."</t>
+  </si>
+  <si>
+    <t>"We asked an IT professional to apply SoCo to FenixEdu (Instituto Su perior Tecnico, 2019), a substantive software used in higher education institutions."</t>
+  </si>
+  <si>
+    <t>Sistemas de Educación Superior</t>
+  </si>
+  <si>
+    <t>"Our example involves a Student Information System (SIS) used in a university (UniXYZ) to process student data for academic purposes. A possible data flow is shown in the diagram in Fig. 1."</t>
+  </si>
+  <si>
+    <t>"the formalism was originally introduced to model cloud-based applications, hence MACM nodes in cluded Software-as-a-Service (SaaS), Infrastructure-as-a-Service (IaaS), and CPS node types, as well as provide, host, use relationships (a simple example is reported in Fig. 2)."</t>
+  </si>
+  <si>
+    <t>Sistemas en la nube, Sector industrial</t>
+  </si>
+  <si>
+    <t>"The ATT&amp;CK framework is currently used by many different organiza tions and industry sectors, including financial, healthcare, retail, and technology, and is a fundamental standardized reference for adversary emulation."</t>
+  </si>
+  <si>
+    <t>"In order to describe our approach in a useful way we use a running example based on the Web Service Security (WS-Security) specification."</t>
+  </si>
+  <si>
+    <t>Servicios Web</t>
+  </si>
+  <si>
+    <t>"Weare going to apply the DSM creation process described in the previous section by using a Web Services domain. It is a very important and interesting domain due to the peculiari ties and high requirements in terms of security demanded in this technology area.The constant evolution and extensive use of software using Web Services put them in the spotlight of multiple threats and attacks."</t>
+  </si>
+  <si>
+    <t>"Exacerbating the aforementioned issues is the fact that typical artifacts of Systems Security Design and Assessment (SSDA) are in the form of ad-hoc documentation, and that these may soon become outdated with respect to the actual design of the system, especially in long-lasting or ongoing system development efforts"</t>
+  </si>
+  <si>
+    <t>Falta de estandarización, Dependencia de expertos, Dificultad de mantenimiento</t>
+  </si>
+  <si>
+    <t>"Accordingly, such approaches require the designer to be proficient with UML modelling as a basis for conducting SSDA. This is unrealistic for SSDA scenarios in which security analysts (alternately, systems security engineers) and systems engineers are not software developers."</t>
+  </si>
+  <si>
+    <t>"But it is not only the safety failure of the security measure, it is also the possibility that the presence of that security measure modifies the way the failures of any other elements of the architecture propagate in a modified manner, i.e. a complete safety analysis of failure modes of new/modified elements as well as redo safety analysis of other existing elements regarding any impact on existing failure modes."</t>
+  </si>
+  <si>
+    <t>Conflicto de objetivos (Safety vs. Security), Falta de automatización, Alta complejidad, Trade-Offs</t>
+  </si>
+  <si>
+    <t>"Trade-Off. Joint engineering team has to prioritize which as pect is more relevant and a trade-off between safety and security measures have to be chosen. The trade-off can be supported by specific safety and security pattern, where a different pattern may be chosen to handle that issue and a compromise has to be achieved."</t>
+  </si>
+  <si>
+    <t>"First, since threat modeling assumes that attacks happen when data flow from one process (i.e., a software component that takes input and either produces output or performs an action) to another, the logic signal flows in the safety pattern need to be translated into directional data flows according to the software architecture implementing this safety logic."</t>
+  </si>
+  <si>
+    <t>"The pattern mechanism of the EA tool seems to work at this stage for bdd diagrams only, which means that the pattern “just reminds you to add needed blocks” and the engineer has to connect them as needed according to the specific context."</t>
+  </si>
+  <si>
+    <t>"There is a need to link these con- cepts to security. The lack of appropriate links between ap- plication domain concepts and security concepts poses three main challenges. First, the security engineer must re-engineer existing solutions. Second, the application designer may not understand domain-specific security solutions. Finally, it is difficult for a system developer to guarantee the availability of security solutions to cover the security requirements of the targeted application using application domain concepts."</t>
+  </si>
+  <si>
+    <t>Brecha de comunicación, Integración tardía, Falta de automatización, Reusabilidad</t>
+  </si>
+  <si>
+    <t>"Most of these techniques and measures are provided in the form of design decisions targeting one stage of the de- velopment lifecycle without effective realization. They should be applied from the very beginning stage of the conception of the system. In addition, the format in which the techniques and measures are presented must be improved to ensure that the provided solutions are storable, reusable and appropriate for the automation of software development and analysis. Fur- thermore, the cost-effective development and certification of the targeted products is a challenge, and the reusability of proven solutions enables cost and time-to-market reductions."</t>
+  </si>
+  <si>
+    <t>"However, implementing appropriate technical controls is often an error-prone and time-consuming process. This is partly due to the limited knowledge of software engineers about privacy and security."</t>
+  </si>
+  <si>
+    <t>Dependencia de expertos, Alta complejidad, Falta de automatización, Integración tardía, Falta de estandarización</t>
+  </si>
+  <si>
+    <t>"In large and complex systems, it is even more challenging to identify where and how priv&amp;sec controls should be implemented."</t>
+  </si>
+  <si>
+    <t>"These approaches are also typically detached from software engineering practices; thus, they can hardly be adopted during the software development life cycle (SDLC)"</t>
+  </si>
+  <si>
+    <t>pág. 3-4</t>
+  </si>
+  <si>
+    <t>"DPPs are expressed using vague and abstract terminology (e.g., ‘‘every reasonable step’’, ‘‘without delay’’), so they can have multiple interpretations and provide limited information about what and how priv&amp;sec controls should be enforced. To identify possible GDPR violations, engineers typically must manually identify and inspect the sequence diagrams where personal data processing occurs. This is cumbersome and error prone, especially in large systems where there may be multiple diagrams to be examined. Finally, engineers may not have the expertise to determine and apply appropriate priv&amp;sec controls (Martin and Kung, 2018; Lopez et al., 2019; Alhazmi and Arachchilage, 2021), which can avoid GDPR violations."</t>
+  </si>
+  <si>
+    <t>"This is mainly due to the limited security skills of common developers/IT project managers and to the typically high costs of security procedures. In fact, while automated tools exist to perform code analysis, vulnerability scanning, or security testing, the manual intervention of security experts is still required not only for security analysis and design, but also to configure and elaborate the output of the security testing tools."</t>
+  </si>
+  <si>
+    <t>Dependencia de expertos, Falta de automatización, Altos costos</t>
+  </si>
+  <si>
+    <t>"Unfortunately, the analysis activities devised during design and de velopment usually need substantial support from human experts and, similarly, security assessment and testing (during the development and after the final deployment) require deep security skills to be performed."</t>
+  </si>
+  <si>
+    <t>"security patterns are human-oriented and as such heavily based on natural language, which implies intrinsic high degrees of impreci sion and ambiguity."</t>
+  </si>
+  <si>
+    <t>Ambigüedad, Falta de automatización, Limitaciones de formato</t>
+  </si>
+  <si>
+    <t>"Security patterns contain UML diagrams that describe how the solution works in a specific context, but the UML diagrams are provided as drawings and therefore miss very important elements and data of the UML models that are not visible.Consequently, this way of providing UML models introduces ambiguity and limits the usefulness of such models for system engineers."</t>
+  </si>
+  <si>
+    <t>pág. 3 sec. 2 párr. 1</t>
+  </si>
+  <si>
+    <t>"While a useful guideline on the importance of clear establishment of rules for any used attack tree model, we chose to adopt the attack tree model accepted by [38, 37], and [35]."</t>
+  </si>
+  <si>
+    <t>pág. 4 sec. 3 párr. 3</t>
+  </si>
+  <si>
+    <t>"Translation of AADL Model to Security Attack Tree (TAMSAT) is focused on the interpretation and translation of AADL model files into a structure that captures the attack profile of the design."</t>
+  </si>
+  <si>
+    <t>pág. 4 sec. 3 párr. 4</t>
+  </si>
+  <si>
+    <t>"Security Model Adversarial Risk-based Tool (SMART) evaluates an AADL model and attack tree representation and pro duces a security risk metric. The tool requires a series of variables that represent costs and value assessments relat ing to defender and attacker."</t>
+  </si>
+  <si>
+    <t>pág. 4 sec. 3 párr. 5</t>
+  </si>
+  <si>
+    <t>"These models are then fed through the TAMSAT tool which identifies potential security vulnerabilities in the designs and generates attack trees that incorporate the design structure and known vulnerabilities. The final step, SMART , evaluates the attack tree structure output from TAMSAT in combination with known vulnerability information in order to produce a Security Risk value in monetary terms."</t>
+  </si>
+  <si>
+    <t>pág. 25 sec. 5.2 fig. 10</t>
+  </si>
+  <si>
+    <t>"Fig. 10  Illustration of the attack trees for IoT home design 06 &amp; 07 side-by-side"</t>
+  </si>
+  <si>
+    <t>pág. 6 sec. S/N párr. 1-2</t>
+  </si>
+  <si>
+    <t>"The task (a.k.a. software) architecture models the software components that implement the components from the logical architecture. In our case, the components of the task archi tecture are given by Docker components. The components of the logical architecture are implemented by containers. Figure 4 shows the task architecture of the our example application system."</t>
+  </si>
+  <si>
+    <t>Task Architecture</t>
+  </si>
+  <si>
+    <t>pág. 5 sec. S/N fig. 4</t>
+  </si>
+  <si>
+    <t>"Fig. 4  Task architecture of running example: The gray area specifies the item boundary"</t>
+  </si>
+  <si>
+    <t>pág. 3 sec. S/N párr. 1</t>
+  </si>
+  <si>
+    <t>"The solution is typically expressed using UML class, sequence, state, and activity diagrams (although we usually need only one or two of these models)."</t>
+  </si>
+  <si>
+    <t>Diagrama de clases UML, Diagrama de secuencia UML, Diagrama de patrones UML</t>
+  </si>
+  <si>
+    <t>pág. 4 sec. S/N párr. 3</t>
+  </si>
+  <si>
+    <t>"Figure 1 is the class model of the Abstract Authenticator, which shows the classes used to perform the activities above."</t>
+  </si>
+  <si>
+    <t>pág. 4 sec. S/N fig. 1</t>
+  </si>
+  <si>
+    <t>"Fig. 1 Class diagram of the abstract authenticator pattern"</t>
+  </si>
+  <si>
+    <t>pág. 4 sec. S/N fig. 2</t>
+  </si>
+  <si>
+    <t>"Fig. 2 Sequence diagram for the use case “authenticate a subject”</t>
+  </si>
+  <si>
+    <t>pág. 5 sec. S/N fig. 3</t>
+  </si>
+  <si>
+    <t>"Fig. 3 Class diagram of the credential-based authenticator pattern"</t>
+  </si>
+  <si>
+    <t>"Fig. 4 Pattern diagram for an authentication hierarchy"</t>
+  </si>
+  <si>
+    <t>pág. 6 sec. S/N fig. 5</t>
+  </si>
+  <si>
+    <t>"Fig. 5 Class model of the X.509-based authenticator"</t>
+  </si>
+  <si>
+    <t>pág. 6 sec. S/N fig. 6</t>
+  </si>
+  <si>
+    <t>"Fig. 6 Class model of the SAML-based authenticator"</t>
+  </si>
+  <si>
+    <t>pág. 6 sec. S/N fig. 7</t>
+  </si>
+  <si>
+    <t>"Fig. 7 Class model of the password-based authenticator"</t>
+  </si>
+  <si>
+    <t>pág. 2 sec. 1 párr. 3</t>
+  </si>
+  <si>
+    <t>"Graph-based threat models mainly include attack graphs [21], which are important technologies for cyber security analysis and vulnerability assessment [26, 27]. Attack graphs can graphically display identifiable attack paths in cyber-attack scenarios and assess the cyber security risks of the target system [13, 28]."</t>
+  </si>
+  <si>
+    <t>pág. 2 sec. 1 párr. 4</t>
+  </si>
+  <si>
+    <t>"In this paper, the attack graph is generated based on the system topology diagram as the input. The system topology diagram [27] is a graphical representation that describes the connection relationship between the components in the system. Topology diagram is an abstract representation method that displays the logical structure and physical connections of each component of the system through intuitive graphical symbols, which can help people better understand and deal with the complex relation ships in the system [27, 30]. It can be used in the early design phase to help designers understand user requirements, analyze and design a secure system architecture, and can also be used to analyze the security state of the system that has been implemented [30, 31]."</t>
+  </si>
+  <si>
+    <t>pág. 9 sec. 3. párr. 20</t>
+  </si>
+  <si>
+    <t>"For this analysis, five distinct topological UAV system models corresponding to the defined 5 T STRIDE levels have been developed."</t>
+  </si>
+  <si>
+    <t>pág. 9 sec. 4 párr. 1</t>
+  </si>
+  <si>
+    <t>"Figures 3–7 show the process of generating the five-level threat models for UAV design."</t>
+  </si>
+  <si>
+    <t>pág. 9-10 sec. 4 párr. 4</t>
+  </si>
+  <si>
+    <t>"Figure 5 shows the application-level trusted model. In this trust level, only the application-level components are considered potential sources of threats, while the operating systems and hardware are classified as trusted components."</t>
+  </si>
+  <si>
+    <t>pág. 9 sec. 3. fig. 3</t>
+  </si>
+  <si>
+    <t>"Fig. 3 System-level model"</t>
+  </si>
+  <si>
+    <t>pág. 10 sec. 4. fig. 4</t>
+  </si>
+  <si>
+    <t>"Fig. 4 Interface-level model"</t>
+  </si>
+  <si>
+    <t>pág. 11 sec. 4. fig. 5</t>
+  </si>
+  <si>
+    <t>"Fig. 5 Application-level model"</t>
+  </si>
+  <si>
+    <t>pág. 12 sec. 4. fig. 6</t>
+  </si>
+  <si>
+    <t>"Fig. 6 Operating-system-level model"</t>
+  </si>
+  <si>
+    <t>pág. 13 sec. 5. fig. 7</t>
+  </si>
+  <si>
+    <t>"Fig. 7 Hardware-level model"</t>
+  </si>
+  <si>
+    <t>"We have called our security risk analysis framework the GAM-TAMSAT-SMART (G-T-S) Framework, and it is made up of three separate tools that effectively allow a user to generate, translate, and evaluate Architecture Analysis &amp; Design Language (AADL) models for their respective Security Risk."</t>
+  </si>
+  <si>
+    <t>AADL</t>
+  </si>
+  <si>
+    <t>"Generate AADL Models (GAM) is focused on the generation of AADL models based on some preconceived user-defined attributes. The tool will create AADL models that contain the bus, data, device, and system definitions that represent the intended model"</t>
+  </si>
+  <si>
+    <t>"Threat Analysis and Risk Assessment (TARA) is a well-known approach used by researchers and practitioners. TARA consists of several activities, including asset identification, threat scenarios, attack paths, and risk treatment decision. The risk treatment decision activity involves selecting appropriate security measures to mitigate the identified threat scenarios."</t>
+  </si>
+  <si>
+    <t>TARA (ISO/SAE 21434), MBSE</t>
+  </si>
+  <si>
+    <t>"This article proposes Security Pattern Synthesis, a Model-Based Systems Engineering (MBSE) plugin for securing cloud architectures."</t>
+  </si>
+  <si>
+    <t>"Finally, we discuss their practical value, including their use in “security by design” and IoT systems design."</t>
+  </si>
+  <si>
+    <t>Security-by-design</t>
+  </si>
+  <si>
+    <t>"Demonstrating the value of ASPs by showing how they can be used to build conceptual models, to derive new patterns, and other possible uses for secure application development, including security by design and IoT systems design."</t>
+  </si>
+  <si>
+    <t>"First, we design an automatic attack graph generation model based on Common Attack Pattern Enumeration and Classification (CAPEC) and MITRE ATT&amp;CK Matrix."</t>
+  </si>
+  <si>
+    <t>CAPEC, MITRE ATT&amp;CK</t>
+  </si>
+  <si>
+    <t>"In this paper, the attack graph threat model generated based on CAPEC2 and ATT&amp;CK Matrix3 is used to deal with the cyber security of enterprise systems."</t>
+  </si>
+  <si>
+    <t>"We design an automatic attack graph generation model based on CAPEC and ATT&amp;CKMatrix, which supports generation of attack graphs based on scene topology information. The model is implemented using the Meta Attack Language (MAL) to ensure the extensibility of the model rules."</t>
+  </si>
+  <si>
+    <t>"STRIDE models threats in away that closely aligns with the motivations of attackers, allowing for more effective identification and mitigation of security risks by starting the threat modeling process near the source of potential threats"</t>
+  </si>
+  <si>
+    <t>"an attacking entity can use a debug inter face to access platform secrets assuming they have limited physical presence and the system has specific UEFI settings."</t>
+  </si>
+  <si>
+    <t>Information Disclosure, Spoofing</t>
+  </si>
+  <si>
+    <t>pág. 22</t>
+  </si>
+  <si>
+    <t>"OleumTech WIO DH2 Wireless Gateway and Sensor Wireless I/O Modules, when BreeZ is used, do not require authentication for reading the site security key, which allows physically proximate attackers to spoof communication by obtaining this key after use of direct hardware access or manual-setup mode."</t>
+  </si>
+  <si>
+    <t>"Services need to be authenticate themselves between each other to avoid spoofing attacks. The transmitted data must be protected against tampering."</t>
+  </si>
+  <si>
+    <t>Spoofing, Tampering, Elevation of Privilege</t>
+  </si>
+  <si>
+    <t>"To protect against elevation of privilege attacks, one would additionally like to authorize the actions of services."</t>
+  </si>
+  <si>
+    <t>pág. 4-5</t>
+  </si>
+  <si>
+    <t>"T1. Present fake or stolen proof of identity, to let the attacker impersonate a legitimate subject and get access to the system. T2. Steal a proof of authentication for later attempts to enter the system. T3. Unauthorized reading of authentication information to obtain a proof of identity. T4. Unauthorized modification of authentication information, to produce disruption. T5. Register a subject that has more privileges using false information and then impersonate that subject."</t>
+  </si>
+  <si>
+    <t>Spoofing, Information Disclosure, Tampering, Elevation of Privilege</t>
+  </si>
+  <si>
+    <t>"More than 3000 important data security incidents have been monitored and reported by the platform, including security vulnerabilities in networked information system databases, intrusion control, and personal information theft and ille gal sales, involving multiple industry institutions, such as e-commerce,internet enterprises, healthcare, and off campus training."</t>
+  </si>
+  <si>
+    <t>Information Disclosure, Unauthorized Access, Advanced Persistent Threat, Phising, Ransomware, DoS</t>
+  </si>
+  <si>
+    <t>"hacker organizations would frequently carry out Advanced Persistent Threat (APT) attacks"</t>
+  </si>
+  <si>
+    <t>pág. 26</t>
+  </si>
+  <si>
+    <t>"The attacker first uses phishing link attacks to inject malicious websites into the company’s employee computers to gain initial access to their company’s network. Then, the attacker further gains access to the OT network and deploys ransomware, encrypt ing data on the OT network to affect specific network assets, and extorting a ransom from the company."</t>
+  </si>
+  <si>
+    <t>"offer ing a mnemonic for six categories of security threats: Spoofing Tampering Repudiation Information Disclosure Denial of Service Elevation of privilege"</t>
+  </si>
+  <si>
+    <t>Spoofing, Tampering, Repudiation, Information Disclosure, Denial of Service, Elevation of Privilege</t>
+  </si>
+  <si>
+    <t>"We exemplify the tools, provide methodologies for required background research, and discuss the results in evaluating a series of IoT Home models using the GTS framework."</t>
+  </si>
+  <si>
+    <t>Sistemas IoT, Sistemas Embebidos</t>
+  </si>
+  <si>
+    <t>"We then apply these techniques and asses a collection of IoT Home models originated from the user-defined attributes of the system."</t>
+  </si>
+  <si>
+    <t>"Whether one is dealing with embedded systems and IoT devices or approaching a more traditional environment of server and database elements, the analysis will require the background research and planning to properly account for potential Security Risk."</t>
+  </si>
+  <si>
+    <t>"The running example is a real cloud application devel oped in a research project on the digitalization and auto mation in avionics systems. The application coordinates unmanned air vehicles (UAVs) and provides services, such as transportation services or search-and-rescue services."</t>
+  </si>
+  <si>
+    <t>Cloud Computing, Avionics</t>
+  </si>
+  <si>
+    <t>"The results show that this approach can effectively support users to threat modeling for large systems, and attack graph analysis results can assist enterprise users to make effective security decisions."</t>
+  </si>
+  <si>
+    <t>Large Systems, Operational Technology</t>
+  </si>
+  <si>
+    <t>"involving multiple industry institutions, such as e-commerce,internet enterprises, healthcare, and off campus training."</t>
+  </si>
+  <si>
+    <t>"the United States Cybersecurity and Infras tructure Security Agency (CISA) reported a cyberattack on the compressed facility Operation Technology (OT) network control system of a natural gas pipeline company"</t>
+  </si>
+  <si>
+    <t>"In this paper, we introduce xT-STRIDE, a framework that integrates computational trust into threat analysis, specifically designed for UAV systems."</t>
+  </si>
+  <si>
+    <t>Avionics, Traffic Monitoring</t>
+  </si>
+  <si>
+    <t>pág. 11</t>
+  </si>
+  <si>
+    <t>"The analysis produced threat counts, as shown in Fig. 8, for the traffic monitoring scenario example."</t>
+  </si>
+  <si>
+    <t>"The second point is that by no means is the set of known vulnerabilities complete. New vulnerabilities are constantly being found and presented to the cyber security community for the purpose of expanding the community’s knowledge and awareness of these issues. However, for these same reasons, some vulnerabilities are unknown due to a variety of potential reasons. Overall modeling vulnerabilities can be difficult, but there is a method by which one can understand them and effectively analyze them."</t>
+  </si>
+  <si>
+    <t>Vulnerabilidades desconocidas, Complejidad de modelado</t>
+  </si>
+  <si>
+    <t>"One would also like to understand the trade-offs between different choices regarding system development and operation, e.g., in the form of additional requirements for certificate man agement, or regarding resource overhead."</t>
+  </si>
+  <si>
+    <t>Trade-offs, Complejidad de mitigación</t>
+  </si>
+  <si>
+    <t>"As one considers multiple threat scenarios and possible miti gations, it becomes a complex task to consider all possible options and to understand how they may be combined and what the trade-offs between different choices are."</t>
+  </si>
+  <si>
+    <t>"There is no algorithm to produce ASPs, abstraction is a human activity which depends on the experience and ability of the pattern builder. Deciding what is really essential in an ASP is not always clear and judgment is necessary"</t>
+  </si>
+  <si>
+    <t>Complejidad de modelado, Altos costos</t>
+  </si>
+  <si>
+    <t>"In general, we must not add in each entity all possible security mechanisms, which results in systems that:
+•Are overly complex, with many redundancies, which bring administrative confusion, a source of possible vulnerabilities.
+•Have a high performance overhead, because of redundant checks.
+•Are costly, because most security mechanisms are COTS components, and they have to be bought and maintained."</t>
+  </si>
+  <si>
+    <t>"Because of the complexity of attack graphs and the large amount of infor mation presented, it is difficult for users to effectively use them to complete threat modeling and threat analysis"</t>
+  </si>
+  <si>
+    <t>Complejidad de modelado, Cobertura incompleta</t>
+  </si>
+  <si>
+    <t>"the rules for generating attack graphs are difficult to extend"</t>
+  </si>
+  <si>
+    <t>"Existing tools require users to provide a large amount of system configuration and vulnerability scanning informa tion as input, and the rules for generating attack graphs are difficult to extend."</t>
+  </si>
+  <si>
+    <t>"the generated attack graphs usually cannot cover all possible attack paths in the system"</t>
+  </si>
+  <si>
+    <t>"the prediction accuracy of the generated attack graph analy sis was poor, and the actual attack path was more than three times different from the predicted results."</t>
+  </si>
+  <si>
+    <t>"the overwhelming amount ofinformation presented in attack graphs makes it difficult for users to effectively utilize them to complete threat modeling"</t>
+  </si>
+  <si>
+    <t>"For the auto matic generation model, the quality of the generated attack graph is closely related to the system topology input by users, and creating the system topology input is also one of the challenges of automatic generation of attack graph."</t>
+  </si>
+  <si>
+    <t>"Applying trust level classification to the STRIDE model creates a more accurate threat list by eliminating false assumptions about the operational environment. In an untrustworthy environ ment, STRIDE would identify more threats by removing pre-established trust assumptions. Conversely, in a trusted environment, xT-STRIDE would result in fewer identified threats owing to the use of trusted components."</t>
+  </si>
+  <si>
+    <t>Trade-offs, Altos costos</t>
+  </si>
+  <si>
+    <t>"In an ideal scenario, it would be optimal to select all components as trusted to maximize security. However, choosing to trust all com ponents would result in very high production costs, which manufacturers typically want to avoid. On the other hand, if no trust level is selected, all components are treated as need ing to be secured, which could lead to a less secure design because securing all components in such an environment may be unfeasible. Essentially, selecting the appropriate trust level in xT-STRIDE is a trade-off between cybersecurity and pro duction costs."</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -806,6 +2624,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -955,11 +2781,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -997,15 +2824,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Énfasis2" xfId="1" builtinId="33"/>
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="15">
@@ -1378,8 +3230,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E288BEBA-8B6C-49E4-B886-0FB0C0B57EEB}" name="Tabla4" displayName="Tabla4" ref="B2:K14" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="B2:K14" xr:uid="{E288BEBA-8B6C-49E4-B886-0FB0C0B57EEB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E288BEBA-8B6C-49E4-B886-0FB0C0B57EEB}" name="Tabla4" displayName="Tabla4" ref="B2:K41" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+  <autoFilter ref="B2:K41" xr:uid="{E288BEBA-8B6C-49E4-B886-0FB0C0B57EEB}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{445888A5-8BAD-4F3A-8313-7286162CDC7D}" name="ID" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{6B2244BE-DDA9-42DD-8E1D-9BDB42A4619D}" name="DOI" dataDxfId="8"/>
@@ -1713,7 +3565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72F8274-AA53-4DBA-B3A2-12204548A951}">
-  <dimension ref="B2:K14"/>
+  <dimension ref="B2:K41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -2144,19 +3996,892 @@
         <v>95</v>
       </c>
     </row>
+    <row r="15" spans="2:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2024</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2022</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="F17" s="5">
+        <v>2019</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2018</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" s="5">
+        <v>2016</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2024</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F21" s="5">
+        <v>2019</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2020</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="F23" s="5">
+        <v>2021</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F24" s="5">
+        <v>2016</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F25" s="5">
+        <v>2020</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F26" s="5">
+        <v>2017</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F27" s="5">
+        <v>2016</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="F28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="F29" s="5">
+        <v>2023</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="F30" s="8">
+        <v>2023</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="F31" s="5">
+        <v>2023</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="F32" s="5">
+        <v>2020</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F33" s="5">
+        <v>2018</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F34" s="5">
+        <v>2024</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F35" s="5">
+        <v>2024</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="F36" s="8">
+        <v>2017</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="F37" s="5">
+        <v>2022</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="F38" s="5">
+        <v>2024</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="F39" s="5">
+        <v>2022</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="F40" s="5">
+        <v>2025</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="F41" s="8">
+        <v>2025</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>427</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C31" r:id="rId1" xr:uid="{17079803-010E-4D2E-8060-59299D26C0EF}"/>
+    <hyperlink ref="C32" r:id="rId2" xr:uid="{85B3CF64-898D-40ED-B437-74F8696140B2}"/>
+    <hyperlink ref="C33" r:id="rId3" xr:uid="{5E2CE71B-02DA-422F-9B31-BD47B8F7654D}"/>
+    <hyperlink ref="C34" r:id="rId4" xr:uid="{5B5A94BC-44DA-469F-ABCE-D258ABBEC594}"/>
+    <hyperlink ref="C35" r:id="rId5" xr:uid="{E3ECD440-3536-45F6-9CE5-F752ACF98B94}"/>
+    <hyperlink ref="C36" r:id="rId6" xr:uid="{EDAA994E-7EED-4482-9D91-EDB6ED26453D}"/>
+    <hyperlink ref="C37" r:id="rId7" xr:uid="{2E12FD51-416B-4E89-848D-FE0B914CA5B6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFFC2FF-C16F-476B-B98C-E2D283C89D52}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -2167,7 +4892,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2185,351 +4910,1339 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B4" s="19"/>
+      <c r="C4" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B4" s="13"/>
-      <c r="C4" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
+      <c r="B6" s="19"/>
       <c r="C6" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="13"/>
+        <v>121</v>
+      </c>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="17" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="19"/>
+      <c r="C8" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="13"/>
-      <c r="C8" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>101</v>
-      </c>
       <c r="D9" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B10" s="19"/>
+      <c r="C10" s="10" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
-      <c r="C10" s="10" t="s">
-        <v>101</v>
-      </c>
       <c r="D10" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E10" s="13"/>
+        <v>143</v>
+      </c>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>158</v>
-      </c>
     </row>
     <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E12" s="12" t="s">
         <v>164</v>
       </c>
+      <c r="E12" s="17" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E13" s="13"/>
+        <v>170</v>
+      </c>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B16" s="19"/>
+      <c r="C16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="18"/>
+      <c r="C18" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="18"/>
+      <c r="C19" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="19"/>
+      <c r="C20" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="19"/>
+      <c r="C22" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B24" s="18"/>
+      <c r="C24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="18"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="18"/>
+      <c r="C25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="19"/>
+      <c r="C26" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="19"/>
+      <c r="C28" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B30" s="18"/>
+      <c r="C30" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="14"/>
-      <c r="C15" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B16" s="13"/>
-      <c r="C16" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="14"/>
-      <c r="C18" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="14"/>
-      <c r="C19" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="13"/>
-      <c r="C20" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="13"/>
-      <c r="C22" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B24" s="14"/>
-      <c r="C24" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="E24" s="14"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="14"/>
-      <c r="C25" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="E25" s="14"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="13"/>
-      <c r="C26" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="E26" s="13"/>
-    </row>
-    <row r="27" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B27" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="13"/>
-      <c r="C28" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="E28" s="13"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B30" s="14"/>
-      <c r="C30" s="10" t="s">
-        <v>108</v>
-      </c>
       <c r="D30" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="19"/>
+      <c r="C31" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="E30" s="14"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="13"/>
-      <c r="C31" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="E31" s="13"/>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B32" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B33" s="18"/>
+      <c r="C33" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="34" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B34" s="18"/>
+      <c r="C34" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="E34" s="18"/>
+    </row>
+    <row r="35" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B35" s="18"/>
+      <c r="C35" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="E35" s="18"/>
+    </row>
+    <row r="36" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B36" s="18"/>
+      <c r="C36" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="E36" s="18"/>
+    </row>
+    <row r="37" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B37" s="19"/>
+      <c r="C37" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B39" s="19"/>
+      <c r="C39" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B40" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B41" s="18"/>
+      <c r="C41" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E41" s="18"/>
+    </row>
+    <row r="42" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B42" s="18"/>
+      <c r="C42" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B43" s="18"/>
+      <c r="C43" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E43" s="18"/>
+    </row>
+    <row r="44" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B44" s="18"/>
+      <c r="C44" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="E44" s="18"/>
+    </row>
+    <row r="45" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B45" s="18"/>
+      <c r="C45" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B46" s="19"/>
+      <c r="C46" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B47" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B48" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B49" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="20"/>
+      <c r="C50" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="E50" s="20"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="20"/>
+      <c r="C51" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="20"/>
+      <c r="C52" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="E52" s="20"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="20"/>
+      <c r="C53" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="E53" s="20"/>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="20"/>
+      <c r="C54" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="E54" s="20"/>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B56" s="19"/>
+      <c r="C56" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B57" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B58" s="18"/>
+      <c r="C58" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="E58" s="18"/>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="18"/>
+      <c r="C59" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="E59" s="18"/>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="19"/>
+      <c r="C60" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B61" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B62" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B63" s="18"/>
+      <c r="C63" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E63" s="18"/>
+    </row>
+    <row r="64" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B64" s="19"/>
+      <c r="C64" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B65" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B66" s="19"/>
+      <c r="C66" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B67" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B68" s="18"/>
+      <c r="C68" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="E68" s="18"/>
+    </row>
+    <row r="69" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B69" s="19"/>
+      <c r="C69" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B70" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B71" s="18"/>
+      <c r="C71" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="E71" s="18"/>
+    </row>
+    <row r="72" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B72" s="19"/>
+      <c r="C72" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B73" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B74" s="18"/>
+      <c r="C74" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="E74" s="18"/>
+    </row>
+    <row r="75" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B75" s="18"/>
+      <c r="C75" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="E75" s="18"/>
+    </row>
+    <row r="76" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B76" s="19"/>
+      <c r="C76" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B77" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B78" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B79" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B80" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B81" s="19"/>
+      <c r="C81" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="E81" s="19"/>
+    </row>
+    <row r="82" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B82" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B83" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="E83" s="17" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B84" s="18"/>
+      <c r="C84" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="E84" s="18"/>
+    </row>
+    <row r="85" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B85" s="19"/>
+      <c r="C85" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="E85" s="19"/>
+    </row>
+    <row r="86" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B86" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B87" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="E87" s="17" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B88" s="18"/>
+      <c r="C88" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="E88" s="18"/>
+    </row>
+    <row r="89" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B89" s="19"/>
+      <c r="C89" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="E89" s="19"/>
+    </row>
+    <row r="90" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B90" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="E90" s="17" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B91" s="18"/>
+      <c r="C91" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="E91" s="18"/>
+    </row>
+    <row r="92" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B92" s="18"/>
+      <c r="C92" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="E92" s="18"/>
+    </row>
+    <row r="93" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B93" s="18"/>
+      <c r="C93" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="E93" s="18"/>
+    </row>
+    <row r="94" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B94" s="19"/>
+      <c r="C94" s="10" t="s">
+        <v>725</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="E94" s="19"/>
+    </row>
+    <row r="95" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B95" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="E95" s="17" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B96" s="19"/>
+      <c r="C96" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="E96" s="19"/>
+    </row>
+    <row r="97" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B97" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B98" s="20"/>
+      <c r="C98" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="E98" s="20"/>
+    </row>
+    <row r="99" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B99" s="20"/>
+      <c r="C99" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="E99" s="20"/>
+    </row>
+    <row r="100" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B100" s="20"/>
+      <c r="C100" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="E100" s="20"/>
+    </row>
+    <row r="101" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B101" s="20"/>
+      <c r="C101" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="E101" s="20"/>
+    </row>
+    <row r="102" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B102" s="20"/>
+      <c r="C102" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="E102" s="20"/>
+    </row>
+    <row r="103" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B103" s="20"/>
+      <c r="C103" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="E103" s="20"/>
+    </row>
+    <row r="104" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B104" s="20"/>
+      <c r="C104" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="E104" s="20"/>
+    </row>
+    <row r="105" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B105" s="20"/>
+      <c r="C105" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="E105" s="20"/>
+    </row>
+    <row r="106" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B106" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="E106" s="20" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="B107" s="20"/>
+      <c r="C107" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="E107" s="20"/>
+    </row>
+    <row r="108" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B108" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="E108" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B109" s="20"/>
+      <c r="C109" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="E109" s="20"/>
+    </row>
+    <row r="110" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B110" s="20"/>
+      <c r="C110" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="E110" s="20"/>
+    </row>
+    <row r="111" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B111" s="20"/>
+      <c r="C111" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>761</v>
+      </c>
+      <c r="E111" s="20"/>
+    </row>
+    <row r="112" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B112" s="20"/>
+      <c r="C112" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="E112" s="20"/>
+    </row>
+    <row r="113" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B113" s="20"/>
+      <c r="C113" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="E113" s="20"/>
+    </row>
+    <row r="114" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B114" s="20"/>
+      <c r="C114" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>767</v>
+      </c>
+      <c r="E114" s="20"/>
+    </row>
+    <row r="115" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B115" s="20"/>
+      <c r="C115" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="E115" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="E7:E8"/>
+  <mergeCells count="60">
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="B108:B115"/>
+    <mergeCell ref="E108:E115"/>
+    <mergeCell ref="B90:B94"/>
+    <mergeCell ref="E90:E94"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="B97:B105"/>
+    <mergeCell ref="E97:E105"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="E83:E85"/>
+    <mergeCell ref="B87:B89"/>
+    <mergeCell ref="E87:E89"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="E67:E69"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="B73:B76"/>
+    <mergeCell ref="E73:E76"/>
+    <mergeCell ref="B57:B60"/>
+    <mergeCell ref="E57:E60"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="E62:E64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="E40:E46"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="E49:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E27:E28"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B17:B20"/>
@@ -2538,14 +6251,12 @@
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="E14:E16"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="E7:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2554,17 +6265,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731F6E18-D794-4621-BC40-E9DDFB179283}">
-  <dimension ref="B2:F18"/>
+  <dimension ref="B2:E65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="94" customWidth="1"/>
     <col min="5" max="5" width="44.5703125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -2577,253 +6287,831 @@
       <c r="E2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F4" s="10"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="19"/>
+      <c r="C8" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="14"/>
-      <c r="C7" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="13"/>
-      <c r="C8" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="2:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
+    </row>
+    <row r="10" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B10" s="19"/>
       <c r="C10" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="2:6" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D15" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B16" s="13"/>
+    </row>
+    <row r="16" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B16" s="19"/>
       <c r="C16" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B20" s="20"/>
+      <c r="C20" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="E20" s="20"/>
+    </row>
+    <row r="21" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B21" s="20"/>
+      <c r="C21" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="E21" s="20"/>
+    </row>
+    <row r="22" spans="2:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B24" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B25" s="19"/>
+      <c r="C25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B27" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B28" s="19"/>
+      <c r="C28" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B29" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B31" s="19"/>
+      <c r="C31" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B33" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B34" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B35" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B37" s="19"/>
+      <c r="C37" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B41" s="18"/>
+      <c r="C41" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="E41" s="18"/>
+    </row>
+    <row r="42" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B42" s="19"/>
+      <c r="C42" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="E42" s="19"/>
+    </row>
+    <row r="43" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B43" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B44" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B45" s="20"/>
+      <c r="C45" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="E45" s="20"/>
+    </row>
+    <row r="46" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B46" s="20"/>
+      <c r="C46" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="E46" s="20"/>
+    </row>
+    <row r="47" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B47" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B48" s="20"/>
+      <c r="C48" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B49" s="20"/>
+      <c r="C49" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B50" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B51" s="18"/>
+      <c r="C51" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B53" s="19"/>
+      <c r="C53" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B54" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B55" s="19"/>
+      <c r="C55" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B56" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>770</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B57" s="20"/>
+      <c r="C57" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="E57" s="20"/>
+    </row>
+    <row r="58" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B58" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B59" s="20"/>
+      <c r="C59" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="E59" s="20"/>
+    </row>
+    <row r="60" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B61" s="20"/>
+      <c r="C61" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="E61" s="20"/>
+    </row>
+    <row r="62" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B62" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B63" s="20"/>
+      <c r="C63" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="E63" s="20"/>
+    </row>
+    <row r="64" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B64" s="20"/>
+      <c r="C64" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="E64" s="20"/>
+    </row>
+    <row r="65" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B65" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>140</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="36">
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="E62:E64"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E27:E28"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2832,17 +7120,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED9B382-3E79-4DA1-BDF0-1D64CD5B368D}">
-  <dimension ref="B2:F18"/>
+  <dimension ref="B2:E66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="100.85546875" customWidth="1"/>
     <col min="5" max="5" width="44.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -2855,251 +7142,835 @@
       <c r="E2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
+    </row>
+    <row r="3" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B4" s="18"/>
+      <c r="C4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B5" s="19"/>
+      <c r="C5" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="D6" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B4" s="14"/>
-      <c r="C4" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-    </row>
-    <row r="5" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B5" s="13"/>
-      <c r="C5" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="10" t="s">
+    </row>
+    <row r="7" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="19"/>
+      <c r="C7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="2:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="2:5" ht="240" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>137</v>
-      </c>
       <c r="E8" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="2:6" ht="345" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="345" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="2:6" ht="75" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="75" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="19"/>
+      <c r="C15" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="13"/>
-      <c r="C15" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E15" s="19"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F18" s="10"/>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B20" s="20"/>
+      <c r="C20" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="E20" s="20"/>
+    </row>
+    <row r="21" spans="2:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="19"/>
+      <c r="C24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B28" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="19"/>
+      <c r="C29" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B32" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="E32" s="10"/>
+    </row>
+    <row r="33" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B33" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B34" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B35" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B36" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B37" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B38" s="22"/>
+      <c r="C38" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="E38" s="22"/>
+    </row>
+    <row r="39" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B39" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="19"/>
+      <c r="C40" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B41" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B42" s="18"/>
+      <c r="C42" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B43" s="19"/>
+      <c r="C43" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B44" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B45" s="18"/>
+      <c r="C45" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B46" s="19"/>
+      <c r="C46" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B47" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B48" s="18"/>
+      <c r="C48" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="E48" s="18"/>
+    </row>
+    <row r="49" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B49" s="19"/>
+      <c r="C49" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B50" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B51" s="18"/>
+      <c r="C51" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="E51" s="18"/>
+    </row>
+    <row r="52" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="19"/>
+      <c r="C52" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="18"/>
+      <c r="C54" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="E54" s="18"/>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="18"/>
+      <c r="C55" s="10" t="s">
+        <v>673</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="E55" s="18"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="19"/>
+      <c r="C56" s="10" t="s">
+        <v>673</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B57" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B58" s="20"/>
+      <c r="C58" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="E58" s="20"/>
+    </row>
+    <row r="59" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B59" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B60" s="20"/>
+      <c r="C60" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="E60" s="20"/>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="20"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="20"/>
+    </row>
+    <row r="63" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B63" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="20"/>
+      <c r="C64" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="E64" s="20"/>
+    </row>
+    <row r="65" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B65" s="20"/>
+      <c r="C65" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="E65" s="20"/>
+    </row>
+    <row r="66" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B66" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>800</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="36">
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="E63:E65"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="E53:E56"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="E28:E29"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3108,17 +7979,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02461388-D6A9-4F45-80B9-B5CDF30F4811}">
-  <dimension ref="B2:F17"/>
+  <dimension ref="B2:E64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="80.140625" customWidth="1"/>
     <col min="5" max="5" width="57.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -3131,238 +8001,825 @@
       <c r="E2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B4" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="12" t="s">
+    </row>
+    <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="19"/>
+      <c r="C5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="13"/>
-      <c r="C5" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="2:5" ht="120" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
+    </row>
+    <row r="8" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B8" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B9" s="19"/>
+      <c r="C9" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="2:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
-      <c r="C9" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="13"/>
+    </row>
+    <row r="11" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B11" s="19"/>
       <c r="C11" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="2:6" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D16" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B22" s="19"/>
+      <c r="C22" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B27" s="19"/>
+      <c r="C27" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B30" s="19"/>
+      <c r="C30" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B31" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B32" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B33" s="19"/>
+      <c r="C33" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B34" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B35" s="19"/>
+      <c r="C35" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B37" s="19"/>
+      <c r="C37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B38" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B39" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B40" s="19"/>
+      <c r="C40" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B41" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="B42" s="19"/>
+      <c r="C42" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="E42" s="19"/>
+    </row>
+    <row r="43" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B43" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B44" s="19"/>
+      <c r="C44" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B45" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B46" s="18"/>
+      <c r="C46" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="E46" s="18"/>
+    </row>
+    <row r="47" spans="2:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="B47" s="19"/>
+      <c r="C47" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B48" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B49" s="19"/>
+      <c r="C49" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B50" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B51" s="19"/>
+      <c r="C51" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>690</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B53" s="19"/>
+      <c r="C53" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B54" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B55" s="20"/>
+      <c r="C55" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="E55" s="20"/>
+    </row>
+    <row r="56" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B56" s="20"/>
+      <c r="C56" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="E56" s="20"/>
+    </row>
+    <row r="57" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B57" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B58" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B59" s="20"/>
+      <c r="C59" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="E59" s="20"/>
+    </row>
+    <row r="60" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B61" s="20"/>
+      <c r="C61" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="E61" s="20"/>
+    </row>
+    <row r="62" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B62" s="20"/>
+      <c r="C62" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="E62" s="20"/>
+    </row>
+    <row r="63" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B63" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B64" s="19"/>
+      <c r="C64" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="E64" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="40">
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="E32:E33"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="E29:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3371,17 +8828,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{587B9B9D-F66D-40A5-A831-E177E996281E}">
-  <dimension ref="B2:F22"/>
+  <dimension ref="B2:E70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="110.85546875" customWidth="1"/>
     <col min="5" max="5" width="30.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -3394,295 +8850,869 @@
       <c r="E2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
+    </row>
+    <row r="3" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B4" s="18"/>
+      <c r="C4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="14"/>
-      <c r="C4" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-    </row>
-    <row r="5" spans="2:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="18"/>
       <c r="C5" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B6" s="19"/>
+      <c r="C6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-    </row>
-    <row r="6" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
+      <c r="E7" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="18"/>
       <c r="C8" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-    </row>
-    <row r="9" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
+        <v>120</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="19"/>
       <c r="C9" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="10" t="s">
+    </row>
+    <row r="12" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B12" s="14"/>
-      <c r="C12" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B13" s="14"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
       <c r="C13" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B14" s="19"/>
+      <c r="C14" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="2:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="B14" s="13"/>
-      <c r="C14" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="120" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="2:6" ht="255" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="255" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="135" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="135" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>124</v>
-      </c>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B29" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B31" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B33" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B34" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B36" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B37" s="18"/>
+      <c r="C37" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B38" s="19"/>
+      <c r="C38" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B40" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B41" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B42" s="19"/>
+      <c r="C42" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="E42" s="19"/>
+    </row>
+    <row r="43" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B43" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B44" s="18"/>
+      <c r="C44" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="E44" s="18"/>
+    </row>
+    <row r="45" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B45" s="18"/>
+      <c r="C45" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B46" s="19"/>
+      <c r="C46" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B47" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B48" s="19"/>
+      <c r="C48" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B49" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B50" s="18"/>
+      <c r="C50" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="E50" s="18"/>
+    </row>
+    <row r="51" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B51" s="18"/>
+      <c r="C51" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="E51" s="18"/>
+    </row>
+    <row r="52" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="B52" s="19"/>
+      <c r="C52" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B53" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B54" s="19"/>
+      <c r="C54" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B55" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B56" s="19"/>
+      <c r="C56" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B57" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>815</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B58" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B59" s="22"/>
+      <c r="C59" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="E59" s="22"/>
+    </row>
+    <row r="60" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B61" s="20"/>
+      <c r="C61" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="E61" s="20"/>
+    </row>
+    <row r="62" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B62" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="20"/>
+      <c r="C63" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="E63" s="20"/>
+    </row>
+    <row r="64" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B64" s="20"/>
+      <c r="C64" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>826</v>
+      </c>
+      <c r="E64" s="20"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="20"/>
+      <c r="C65" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="E65" s="20"/>
+    </row>
+    <row r="66" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B66" s="20"/>
+      <c r="C66" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>828</v>
+      </c>
+      <c r="E66" s="20"/>
+    </row>
+    <row r="67" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B67" s="20"/>
+      <c r="C67" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="E67" s="20"/>
+    </row>
+    <row r="68" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B68" s="20"/>
+      <c r="C68" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>830</v>
+      </c>
+      <c r="E68" s="20"/>
+    </row>
+    <row r="69" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B69" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>831</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B70" s="19"/>
+      <c r="C70" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="E70" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="28">
+    <mergeCell ref="B62:B68"/>
+    <mergeCell ref="E62:E68"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="E49:E52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="E43:E46"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="E11:E14"/>
-    <mergeCell ref="F11:F14"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="E3:E6"/>
-    <mergeCell ref="F3:F6"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
